--- a/guia.xlsx
+++ b/guia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Documents\casas espiritas - 23-02-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{861B7139-9853-416A-8357-A29DBDBFDFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E92A0E1-A919-494C-B084-EDE9C87A3639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="7440" yWindow="0" windowWidth="30960" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="654">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -6413,6 +6413,27 @@
       </rPr>
       <t>Rua Valentim Bertelli 640 - Bairro São Miguel</t>
     </r>
+  </si>
+  <si>
+    <t>CIDADE DO CENTRO ESPIRITA</t>
+  </si>
+  <si>
+    <t>ENDERECO</t>
+  </si>
+  <si>
+    <t>PALESTRA PUBLICA</t>
+  </si>
+  <si>
+    <t>CELULAR</t>
+  </si>
+  <si>
+    <t>RESPONSAVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOME FANTASIA </t>
   </si>
 </sst>
 </file>
@@ -6971,7 +6992,7 @@
     <col min="3" max="3" width="42.5703125" style="7"/>
     <col min="4" max="4" width="36.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61.140625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="38.140625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="37.140625" style="29" customWidth="1"/>
     <col min="7" max="7" width="22.5703125" style="29" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="42.5703125" style="7"/>
@@ -6979,25 +7000,25 @@
   <sheetData>
     <row r="1" spans="2:9" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>652</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>647</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>648</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>649</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>651</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>650</v>
       </c>
       <c r="I1" s="2"/>
     </row>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E92A0E1-A919-494C-B084-EDE9C87A3639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E8FC51-70FC-4E1B-9D84-2DC9B03AA478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="0" windowWidth="30960" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -6415,25 +6415,25 @@
     </r>
   </si>
   <si>
-    <t>CIDADE DO CENTRO ESPIRITA</t>
-  </si>
-  <si>
-    <t>ENDERECO</t>
-  </si>
-  <si>
-    <t>PALESTRA PUBLICA</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>RESPONSAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOME </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOME FANTASIA </t>
+    <t xml:space="preserve">A:NOME FANTASIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B:NOME </t>
+  </si>
+  <si>
+    <t>C:CIDADE DO CENTRO ESPIRITA</t>
+  </si>
+  <si>
+    <t>D:ENDERECO</t>
+  </si>
+  <si>
+    <t>E:PALESTRA PUBLICA</t>
+  </si>
+  <si>
+    <t>F:RESPONSAVEL</t>
+  </si>
+  <si>
+    <t>G:CELULAR</t>
   </si>
 </sst>
 </file>
@@ -7000,25 +7000,25 @@
   <sheetData>
     <row r="1" spans="2:9" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>653</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>650</v>
       </c>
       <c r="I1" s="2"/>
     </row>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E8FC51-70FC-4E1B-9D84-2DC9B03AA478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED92AE4A-012E-49C3-A9CA-D5DCAE44B547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="0" windowWidth="30960" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="0" yWindow="1050" windowWidth="30960" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -6415,25 +6415,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">A:NOME FANTASIA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B:NOME </t>
-  </si>
-  <si>
-    <t>C:CIDADE DO CENTRO ESPIRITA</t>
-  </si>
-  <si>
-    <t>D:ENDERECO</t>
-  </si>
-  <si>
-    <t>E:PALESTRA PUBLICA</t>
-  </si>
-  <si>
-    <t>F:RESPONSAVEL</t>
-  </si>
-  <si>
-    <t>G:CELULAR</t>
+    <t xml:space="preserve">A,NOME FANTASIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B,NOME </t>
+  </si>
+  <si>
+    <t>C,CIDADE DO CENTRO ESPIRITA</t>
+  </si>
+  <si>
+    <t>D,ENDERECO</t>
+  </si>
+  <si>
+    <t>E,PALESTRA PUBLICA</t>
+  </si>
+  <si>
+    <t>F,RESPONSAVEL</t>
+  </si>
+  <si>
+    <t>G,CELULAR</t>
   </si>
 </sst>
 </file>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED92AE4A-012E-49C3-A9CA-D5DCAE44B547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B145FE74-294D-478C-BE73-FF96B12BEDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1050" windowWidth="30960" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="6390" yWindow="0" windowWidth="32655" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="650">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -3280,18 +3281,6 @@
   <si>
     <r>
       <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.facebook.com/aeluzriopreto</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="12"/>
         <rFont val="Arial MT"/>
         <family val="2"/>
@@ -3335,18 +3324,6 @@
   <si>
     <r>
       <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.facebook.com/aeaksjrp</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="12"/>
         <rFont val="Arial MT"/>
         <family val="2"/>
@@ -4020,18 +3997,6 @@
   <si>
     <r>
       <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.facebook.com/cefasjrp</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="12"/>
         <rFont val="Arial MT"/>
         <family val="2"/>
@@ -4573,18 +4538,6 @@
   <si>
     <r>
       <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.facebook.com/chicoxavierriopreto</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="12"/>
         <rFont val="Arial MT"/>
         <family val="2"/>
@@ -6415,44 +6368,38 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">A,NOME FANTASIA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B,NOME </t>
-  </si>
-  <si>
-    <t>C,CIDADE DO CENTRO ESPIRITA</t>
-  </si>
-  <si>
-    <t>D,ENDERECO</t>
-  </si>
-  <si>
-    <t>E,PALESTRA PUBLICA</t>
-  </si>
-  <si>
-    <t>F,RESPONSAVEL</t>
-  </si>
-  <si>
-    <t>G,CELULAR</t>
+    <t xml:space="preserve">NOME FANTASIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOME </t>
+  </si>
+  <si>
+    <t>CIDADE DO CENTRO ESPIRITA</t>
+  </si>
+  <si>
+    <t>ENDERECO</t>
+  </si>
+  <si>
+    <t>PALESTRA PUBLICA</t>
+  </si>
+  <si>
+    <t>RESPONSAVEL</t>
+  </si>
+  <si>
+    <t>CELULAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Lucida Sans Unicode"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -6482,22 +6429,9 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial MT"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF202124"/>
       <name val="Arial MT"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -6505,48 +6439,23 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Lucida Sans Unicode"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4F2D2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0D9FA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F880"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84EEFC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -6561,93 +6470,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -6984,3122 +6854,2988 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4002065-77F3-44D2-ACFF-818DBCD21AC8}">
-  <dimension ref="B1:I130"/>
+  <dimension ref="B1:H130"/>
   <sheetFormatPr defaultColWidth="42.5703125" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="42.5703125" style="7"/>
-    <col min="4" max="4" width="36.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.140625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="42.5703125" style="7"/>
+    <col min="1" max="1" width="12.42578125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="42.5703125" style="6"/>
+    <col min="4" max="4" width="36.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.140625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="37.140625" style="16" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="42.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B3" s="8" t="s">
+    </row>
+    <row r="3" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="4" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="7">
         <v>17991739729</v>
       </c>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B5" s="11" t="s">
+    </row>
+    <row r="5" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="6" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B7" s="11" t="s">
+    </row>
+    <row r="7" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="4">
         <v>17996164007</v>
       </c>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="8" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="7">
         <v>17992105513</v>
       </c>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B9" s="8" t="s">
+    </row>
+    <row r="9" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B10" s="4" t="s">
+    </row>
+    <row r="10" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B11" s="8" t="s">
+    </row>
+    <row r="11" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="12" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B13" s="8" t="s">
+    </row>
+    <row r="13" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B14" s="4" t="s">
+    </row>
+    <row r="14" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B15" s="13" t="s">
+    </row>
+    <row r="15" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="4">
         <v>17996707811</v>
       </c>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B16" s="4" t="s">
+    </row>
+    <row r="16" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="7">
         <v>17981625858</v>
       </c>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B17" s="13" t="s">
+    </row>
+    <row r="17" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B18" s="4" t="s">
+    </row>
+    <row r="18" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="7">
         <v>1732699990</v>
       </c>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B19" s="8" t="s">
+    </row>
+    <row r="19" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B19" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="4">
         <v>17991385400</v>
       </c>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B20" s="4" t="s">
+    </row>
+    <row r="20" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="7">
         <v>17992731001</v>
       </c>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B21" s="8" t="s">
+    </row>
+    <row r="21" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B22" s="4" t="s">
+    </row>
+    <row r="22" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B23" s="8" t="s">
+    </row>
+    <row r="23" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="4">
         <v>17991019999</v>
       </c>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B24" s="4" t="s">
+    </row>
+    <row r="24" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B25" s="8" t="s">
+    </row>
+    <row r="25" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B26" s="4" t="s">
+    </row>
+    <row r="26" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="7">
         <v>17996487770</v>
       </c>
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B27" s="16" t="s">
+    </row>
+    <row r="27" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="4">
         <v>17991436228</v>
       </c>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B28" s="4" t="s">
+    </row>
+    <row r="28" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="I28" s="6"/>
-    </row>
-    <row r="29" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B29" s="16" t="s">
+    </row>
+    <row r="29" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B29" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="4">
         <v>17981671066</v>
       </c>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B30" s="4" t="s">
+    </row>
+    <row r="30" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="7">
         <v>17997685797</v>
       </c>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B31" s="16" t="s">
+    </row>
+    <row r="31" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B31" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B32" s="4" t="s">
+    </row>
+    <row r="32" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B32" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="7">
         <v>17996369299</v>
       </c>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B33" s="16" t="s">
+    </row>
+    <row r="33" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B33" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="4">
         <v>17992296835</v>
       </c>
-      <c r="I33" s="6"/>
-    </row>
-    <row r="34" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B34" s="4" t="s">
+    </row>
+    <row r="34" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B34" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="7">
         <v>17997762047</v>
       </c>
-      <c r="I34" s="6"/>
-    </row>
-    <row r="35" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B35" s="16" t="s">
+    </row>
+    <row r="35" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B35" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G35" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="4">
         <v>17988298392</v>
       </c>
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B36" s="4" t="s">
+    </row>
+    <row r="36" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B36" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="7">
         <v>17988082952</v>
       </c>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B37" s="16" t="s">
+    </row>
+    <row r="37" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B37" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="4">
         <v>17996170113</v>
       </c>
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B38" s="4" t="s">
+    </row>
+    <row r="38" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B38" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="7">
         <v>17991133571</v>
       </c>
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B39" s="16" t="s">
+    </row>
+    <row r="39" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B39" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="17">
+      <c r="H39" s="4">
         <v>17997196510</v>
       </c>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B40" s="4" t="s">
+    </row>
+    <row r="40" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B40" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="I40" s="6"/>
-    </row>
-    <row r="41" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B41" s="8" t="s">
+    </row>
+    <row r="41" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B41" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="4">
         <v>17997212303</v>
       </c>
-      <c r="I41" s="6"/>
-    </row>
-    <row r="42" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B42" s="4" t="s">
+    </row>
+    <row r="42" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B42" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B43" s="8" t="s">
+    </row>
+    <row r="43" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B43" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="4">
         <v>17981170059</v>
       </c>
-      <c r="I43" s="6"/>
-    </row>
-    <row r="44" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B44" s="4" t="s">
+    </row>
+    <row r="44" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B44" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="I44" s="6"/>
-    </row>
-    <row r="45" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B45" s="8" t="s">
+    </row>
+    <row r="45" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B45" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="4">
         <v>17996015188</v>
       </c>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B46" s="4" t="s">
+    </row>
+    <row r="46" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B46" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="I46" s="6"/>
-    </row>
-    <row r="47" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B47" s="8" t="s">
+    </row>
+    <row r="47" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B47" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="I47" s="6"/>
-    </row>
-    <row r="48" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B48" s="4" t="s">
+    </row>
+    <row r="48" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B48" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="7">
         <v>17992170608</v>
       </c>
-      <c r="I48" s="6"/>
-    </row>
-    <row r="49" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B49" s="13" t="s">
+    </row>
+    <row r="49" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B49" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E49" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="H49" s="14" t="s">
+      <c r="H49" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="I49" s="6"/>
-    </row>
-    <row r="50" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B50" s="4" t="s">
+    </row>
+    <row r="50" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B50" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="H50" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="I50" s="6"/>
-    </row>
-    <row r="51" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B51" s="13" t="s">
+    </row>
+    <row r="51" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B51" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G51" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="H51" s="14" t="s">
+      <c r="H51" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="I51" s="6"/>
-    </row>
-    <row r="52" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B52" s="4" t="s">
+    </row>
+    <row r="52" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B52" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="7">
         <v>1732818196</v>
       </c>
-      <c r="I52" s="6"/>
-    </row>
-    <row r="53" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B53" s="13" t="s">
+    </row>
+    <row r="53" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B53" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="H53" s="14" t="s">
+      <c r="H53" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="I53" s="6"/>
-    </row>
-    <row r="54" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B54" s="4" t="s">
+    </row>
+    <row r="54" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B54" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H54" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="I54" s="6"/>
-    </row>
-    <row r="55" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B55" s="13" t="s">
+    </row>
+    <row r="55" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B55" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E55" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="G55" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="H55" s="14" t="s">
+      <c r="H55" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="I55" s="6"/>
-    </row>
-    <row r="56" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B56" s="4" t="s">
+    </row>
+    <row r="56" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B56" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H56" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="I56" s="6"/>
-    </row>
-    <row r="57" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B57" s="8" t="s">
+    </row>
+    <row r="57" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B57" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H57" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="I57" s="6"/>
-    </row>
-    <row r="58" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B58" s="4" t="s">
+    </row>
+    <row r="58" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B58" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="7">
         <v>17997283279</v>
       </c>
-      <c r="I58" s="6"/>
-    </row>
-    <row r="59" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B59" s="8" t="s">
+    </row>
+    <row r="59" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B59" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="H59" s="9" t="s">
+      <c r="H59" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="I59" s="6"/>
-    </row>
-    <row r="60" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B60" s="4" t="s">
+    </row>
+    <row r="60" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B60" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="H60" s="5" t="s">
+      <c r="H60" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="I60" s="6"/>
-    </row>
-    <row r="61" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B61" s="8" t="s">
+    </row>
+    <row r="61" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B61" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="H61" s="9" t="s">
+      <c r="H61" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="I61" s="6"/>
-    </row>
-    <row r="62" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B62" s="4" t="s">
+    </row>
+    <row r="62" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B62" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="7">
         <v>17997110972</v>
       </c>
-      <c r="I62" s="6"/>
-    </row>
-    <row r="63" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B63" s="18" t="s">
+    </row>
+    <row r="63" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B63" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="F63" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="G63" s="19" t="s">
+      <c r="G63" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="H63" s="19" t="s">
+      <c r="H63" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="I63" s="6"/>
-    </row>
-    <row r="64" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B64" s="4" t="s">
+    </row>
+    <row r="64" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B64" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="H64" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="I64" s="4" t="s">
+    </row>
+    <row r="65" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B65" s="3" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="65" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B65" s="18" t="s">
+      <c r="C65" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="D65" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="F65" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H65" s="4">
+        <v>1732351010</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B66" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E65" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="F65" s="20" t="s">
-        <v>334</v>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="H65" s="19">
-        <v>1732351010</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B66" s="4" t="s">
+      <c r="E66" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="F66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="H66" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B67" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="F66" s="5" t="s">
+      <c r="E67" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B68" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B69" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B70" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B71" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H71" s="4">
+        <v>17997727089</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B72" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B73" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B74" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B75" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B76" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B77" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B78" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B79" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B80" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="H80" s="7">
+        <v>17991167827</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B81" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B82" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="I66" s="6"/>
-    </row>
-    <row r="67" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B67" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="D67" s="19" t="s">
+      <c r="G82" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B83" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E67" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="H67" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="I67" s="6"/>
-    </row>
-    <row r="68" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B68" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="D68" s="5" t="s">
+      <c r="E83" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B84" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="F68" s="5" t="s">
+      <c r="E84" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B85" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B86" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="I68" s="6"/>
-    </row>
-    <row r="69" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B69" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="D69" s="19" t="s">
+      <c r="G86" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="H86" s="7">
+        <v>17996021994</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B87" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E69" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="H69" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="I69" s="6"/>
-    </row>
-    <row r="70" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B70" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="D70" s="5" t="s">
+      <c r="E87" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="H87" s="4">
+        <v>17991251239</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B88" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="F70" s="5" t="s">
+      <c r="E88" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B89" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B90" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B91" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F91" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="I70" s="6"/>
-    </row>
-    <row r="71" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B71" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="C71" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="D71" s="19" t="s">
+      <c r="G91" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B92" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E71" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="H71" s="19">
-        <v>17997727089</v>
-      </c>
-      <c r="I71" s="6"/>
-    </row>
-    <row r="72" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B72" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="D72" s="5" t="s">
+      <c r="E92" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B93" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="F72" s="5" t="s">
+      <c r="E93" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F93" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="I72" s="6"/>
-    </row>
-    <row r="73" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B73" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D73" s="19" t="s">
+      <c r="G93" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B94" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E73" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="F73" s="19" t="s">
+      <c r="E94" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H94" s="7">
+        <v>1732348032</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B95" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="H95" s="4">
+        <v>17996684410</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B96" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G73" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="H73" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="I73" s="6"/>
-    </row>
-    <row r="74" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B74" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="D74" s="5" t="s">
+      <c r="G96" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B97" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="F74" s="5" t="s">
+      <c r="E97" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B98" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B99" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B100" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B101" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="I74" s="6"/>
-    </row>
-    <row r="75" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B75" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="C75" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="D75" s="19" t="s">
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="2:8" ht="14.45" hidden="1" customHeight="1">
+      <c r="B102" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G102" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B103" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E75" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="F75" s="19" t="s">
+      <c r="E103" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="H103" s="4">
+        <v>17981532805</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B104" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B105" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B106" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B107" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B108" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B109" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="H109" s="4">
+        <v>17981692483</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B110" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B111" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G75" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="H75" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="I75" s="6"/>
-    </row>
-    <row r="76" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B76" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D76" s="5" t="s">
+      <c r="G111" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B112" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="I76" s="6"/>
-    </row>
-    <row r="77" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B77" s="18" t="s">
+      <c r="E112" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B113" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E113" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C77" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="D77" s="19" t="s">
+      <c r="F113" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B114" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E77" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="H77" s="19" t="s">
-        <v>398</v>
-      </c>
-      <c r="I77" s="6"/>
-    </row>
-    <row r="78" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B78" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="D78" s="5" t="s">
+      <c r="E114" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B115" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B79" s="18" t="s">
-        <v>406</v>
-      </c>
-      <c r="C79" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="D79" s="19" t="s">
+      <c r="E115" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B116" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E79" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="F79" s="19" t="s">
+      <c r="E116" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G116" s="14" t="s">
+        <v>581</v>
+      </c>
+      <c r="H116" s="14" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B117" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G79" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="H79" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="I79" s="6"/>
-    </row>
-    <row r="80" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B80" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="D80" s="5" t="s">
+      <c r="G117" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B118" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E80" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="F80" s="5" t="s">
+      <c r="E118" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="H118" s="7">
+        <v>1732247602</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B119" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G120" s="15"/>
+      <c r="H120" s="5"/>
+    </row>
+    <row r="121" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B121" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B122" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B123" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B124" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G124" s="15"/>
+      <c r="H124" s="4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B125" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="F125" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="H80" s="10">
-        <v>17991167827</v>
-      </c>
-      <c r="I80" s="6"/>
-    </row>
-    <row r="81" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B81" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="F81" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="G81" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="H81" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="I81" s="6"/>
-    </row>
-    <row r="82" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B82" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="F82" s="5" t="s">
+      <c r="G125" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B126" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G126" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B127" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="F127" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="I82" s="6"/>
-    </row>
-    <row r="83" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B83" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>427</v>
-      </c>
-      <c r="D83" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="F83" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G83" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="H83" s="19" t="s">
-        <v>430</v>
-      </c>
-      <c r="I83" s="6"/>
-    </row>
-    <row r="84" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B84" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I84" s="6"/>
-    </row>
-    <row r="85" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B85" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>438</v>
-      </c>
-      <c r="D85" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E85" s="18" t="s">
-        <v>439</v>
-      </c>
-      <c r="F85" s="19" t="s">
+      <c r="G127" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B128" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" ht="14.45" customHeight="1">
+      <c r="B129" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="F129" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G85" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="H85" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="I85" s="6"/>
-    </row>
-    <row r="86" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B86" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="H86" s="10">
-        <v>17996021994</v>
-      </c>
-      <c r="I86" s="6"/>
-    </row>
-    <row r="87" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B87" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="D87" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>447</v>
-      </c>
-      <c r="F87" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="G87" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="H87" s="19">
-        <v>17991251239</v>
-      </c>
-      <c r="I87" s="6"/>
-    </row>
-    <row r="88" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B88" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="I88" s="6"/>
-    </row>
-    <row r="89" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B89" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="C89" s="18" t="s">
-        <v>455</v>
-      </c>
-      <c r="D89" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="F89" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="G89" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="H89" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B90" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="I90" s="6"/>
-    </row>
-    <row r="91" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B91" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="C91" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="D91" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E91" s="18" t="s">
-        <v>468</v>
-      </c>
-      <c r="F91" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G91" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="H91" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="I91" s="6"/>
-    </row>
-    <row r="92" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B92" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="I92" s="6"/>
-    </row>
-    <row r="93" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B93" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="C93" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="D93" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E93" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="F93" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G93" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="H93" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="I93" s="6"/>
-    </row>
-    <row r="94" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B94" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="H94" s="10">
-        <v>1732348032</v>
-      </c>
-      <c r="I94" s="6"/>
-    </row>
-    <row r="95" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B95" s="18" t="s">
-        <v>486</v>
-      </c>
-      <c r="C95" s="18" t="s">
-        <v>487</v>
-      </c>
-      <c r="D95" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="F95" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G95" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="H95" s="19">
-        <v>17996684410</v>
-      </c>
-      <c r="I95" s="6"/>
-    </row>
-    <row r="96" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B96" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="I96" s="6"/>
-    </row>
-    <row r="97" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B97" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="C97" s="18" t="s">
-        <v>495</v>
-      </c>
-      <c r="D97" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E97" s="18" t="s">
-        <v>496</v>
-      </c>
-      <c r="F97" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="G97" s="19" t="s">
-        <v>497</v>
-      </c>
-      <c r="H97" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="I97" s="6"/>
-    </row>
-    <row r="98" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B98" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="I98" s="6"/>
-    </row>
-    <row r="99" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B99" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="C99" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="D99" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E99" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="F99" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G99" s="19" t="s">
-        <v>507</v>
-      </c>
-      <c r="H99" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="I99" s="6"/>
-    </row>
-    <row r="100" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B100" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="I100" s="6"/>
-    </row>
-    <row r="101" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B101" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="C101" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="D101" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E101" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="F101" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G101" s="19"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="6"/>
-    </row>
-    <row r="102" spans="2:9" ht="14.45" hidden="1" customHeight="1">
-      <c r="B102" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C102" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D102" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="E102" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G102" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="I102" s="6"/>
-    </row>
-    <row r="103" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B103" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="C103" s="18" t="s">
-        <v>518</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E103" s="18" t="s">
-        <v>519</v>
-      </c>
-      <c r="F103" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="H103" s="19">
-        <v>17981532805</v>
-      </c>
-      <c r="I103" s="6"/>
-    </row>
-    <row r="104" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B104" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="I104" s="6"/>
-    </row>
-    <row r="105" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B105" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="C105" s="18" t="s">
-        <v>527</v>
-      </c>
-      <c r="D105" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E105" s="18" t="s">
-        <v>528</v>
-      </c>
-      <c r="F105" s="19" t="s">
-        <v>529</v>
-      </c>
-      <c r="G105" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="H105" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="I105" s="6"/>
-    </row>
-    <row r="106" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B106" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="H106" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="I106" s="6"/>
-    </row>
-    <row r="107" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B107" s="18" t="s">
-        <v>535</v>
-      </c>
-      <c r="C107" s="18" t="s">
-        <v>536</v>
-      </c>
-      <c r="D107" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E107" s="18" t="s">
-        <v>537</v>
-      </c>
-      <c r="F107" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G107" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="H107" s="19" t="s">
-        <v>539</v>
-      </c>
-      <c r="I107" s="6"/>
-    </row>
-    <row r="108" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B108" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="I108" s="6"/>
-    </row>
-    <row r="109" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B109" s="18" t="s">
-        <v>546</v>
-      </c>
-      <c r="C109" s="18" t="s">
-        <v>547</v>
-      </c>
-      <c r="D109" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E109" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="F109" s="19" t="s">
-        <v>549</v>
-      </c>
-      <c r="G109" s="19" t="s">
-        <v>550</v>
-      </c>
-      <c r="H109" s="19">
-        <v>17981692483</v>
-      </c>
-      <c r="I109" s="6"/>
-    </row>
-    <row r="110" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B110" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="H110" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="I110" s="6"/>
-    </row>
-    <row r="111" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B111" s="18" t="s">
-        <v>556</v>
-      </c>
-      <c r="C111" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="D111" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E111" s="18" t="s">
-        <v>558</v>
-      </c>
-      <c r="F111" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G111" s="19" t="s">
-        <v>559</v>
-      </c>
-      <c r="H111" s="19" t="s">
-        <v>560</v>
-      </c>
-      <c r="I111" s="6"/>
-    </row>
-    <row r="112" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B112" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="I112" s="6"/>
-    </row>
-    <row r="113" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B113" s="18" t="s">
-        <v>566</v>
-      </c>
-      <c r="C113" s="18" t="s">
-        <v>567</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E113" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="F113" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G113" s="19" t="s">
-        <v>568</v>
-      </c>
-      <c r="H113" s="19" t="s">
-        <v>569</v>
-      </c>
-      <c r="I113" s="6"/>
-    </row>
-    <row r="114" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B114" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="I114" s="6"/>
-    </row>
-    <row r="115" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B115" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="C115" s="18" t="s">
-        <v>577</v>
-      </c>
-      <c r="D115" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E115" s="18" t="s">
-        <v>578</v>
-      </c>
-      <c r="F115" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G115" s="19" t="s">
-        <v>579</v>
-      </c>
-      <c r="H115" s="19" t="s">
-        <v>580</v>
-      </c>
-      <c r="I115" s="6"/>
-    </row>
-    <row r="116" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B116" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="G116" s="26" t="s">
-        <v>585</v>
-      </c>
-      <c r="H116" s="26" t="s">
-        <v>586</v>
-      </c>
-      <c r="I116" s="6"/>
-    </row>
-    <row r="117" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B117" s="18" t="s">
-        <v>587</v>
-      </c>
-      <c r="C117" s="18" t="s">
-        <v>588</v>
-      </c>
-      <c r="D117" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E117" s="18" t="s">
-        <v>589</v>
-      </c>
-      <c r="F117" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G117" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="H117" s="19" t="s">
-        <v>590</v>
-      </c>
-      <c r="I117" s="6"/>
-    </row>
-    <row r="118" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B118" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="H118" s="10">
-        <v>1732247602</v>
-      </c>
-      <c r="I118" s="6"/>
-    </row>
-    <row r="119" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B119" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="C119" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="D119" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E119" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="F119" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G119" s="19" t="s">
-        <v>598</v>
-      </c>
-      <c r="H119" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="I119" s="6"/>
-    </row>
-    <row r="120" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B120" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G120" s="27"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-    </row>
-    <row r="121" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B121" s="18" t="s">
-        <v>602</v>
-      </c>
-      <c r="C121" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="D121" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="E121" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G121" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="H121" s="19" t="s">
-        <v>606</v>
-      </c>
-      <c r="I121" s="6"/>
-    </row>
-    <row r="122" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B122" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="H122" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="I122" s="6"/>
-    </row>
-    <row r="123" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B123" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="I123" s="6"/>
-    </row>
-    <row r="124" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B124" s="11" t="s">
-        <v>618</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="D124" s="12" t="s">
-        <v>620</v>
-      </c>
-      <c r="E124" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="F124" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G124" s="28"/>
-      <c r="H124" s="12" t="s">
-        <v>622</v>
-      </c>
-      <c r="I124" s="6"/>
-    </row>
-    <row r="125" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B125" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="H125" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="I125" s="6"/>
-    </row>
-    <row r="126" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B126" s="11" t="s">
-        <v>628</v>
-      </c>
-      <c r="C126" s="11" t="s">
-        <v>629</v>
-      </c>
-      <c r="D126" s="12" t="s">
-        <v>620</v>
-      </c>
-      <c r="E126" s="11" t="s">
-        <v>630</v>
-      </c>
-      <c r="F126" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G126" s="28" t="s">
-        <v>631</v>
-      </c>
-      <c r="H126" s="12" t="s">
-        <v>632</v>
-      </c>
-      <c r="I126" s="6"/>
-    </row>
-    <row r="127" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B127" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="H127" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="I127" s="6"/>
-    </row>
-    <row r="128" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B128" s="13" t="s">
+      <c r="G129" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="C128" s="13" t="s">
+      <c r="H129" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="D128" s="14" t="s">
-        <v>640</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>641</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G128" s="14" t="s">
-        <v>642</v>
-      </c>
-      <c r="H128" s="14" t="s">
-        <v>643</v>
-      </c>
-      <c r="I128" s="6"/>
-    </row>
-    <row r="129" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B129" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="H129" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="I129" s="6"/>
-    </row>
-    <row r="130" spans="2:9" ht="14.45" customHeight="1"/>
+    </row>
+    <row r="130" spans="2:8" ht="14.45" customHeight="1"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I64" r:id="rId1" xr:uid="{842B9B00-7735-4C53-AE3C-5D7666752F71}"/>
-    <hyperlink ref="I65" r:id="rId2" xr:uid="{C53C13A4-6DF5-4FFB-AD12-776E8533AEA1}"/>
-    <hyperlink ref="I78" r:id="rId3" xr:uid="{3DE08C26-A8F7-49B5-A11B-5F9C04DCD158}"/>
-    <hyperlink ref="I89" r:id="rId4" xr:uid="{9D4F8A76-1BBB-4142-B6C7-94E0F8B7CCDD}"/>
-  </hyperlinks>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F04C347-9A55-4468-B43D-6DB12D689605}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B145FE74-294D-478C-BE73-FF96B12BEDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0612093-FDBA-4988-A8A6-AB6CB0476439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6390" yWindow="0" windowWidth="32655" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="8520" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -869,16 +869,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Toda segunda 5ª feira do</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Luciana</t>
     </r>
   </si>
@@ -3348,16 +3338,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Avenida Mirassolândia 1950 - Jardim Mugnani</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Israel Cestari</t>
     </r>
   </si>
@@ -6387,6 +6367,12 @@
   </si>
   <si>
     <t>CELULAR</t>
+  </si>
+  <si>
+    <t>Avenida Mirassolândia 1950 - Jardim Ana Celia</t>
+  </si>
+  <si>
+    <t>Toda segunda 5ª feira do</t>
   </si>
 </sst>
 </file>
@@ -6870,25 +6856,25 @@
   <sheetData>
     <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="14.45" customHeight="1">
@@ -7226,11 +7212,11 @@
       <c r="E16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="H16" s="7">
         <v>17981625858</v>
@@ -7238,45 +7224,45 @@
     </row>
     <row r="17" spans="2:8" ht="14.45" customHeight="1">
       <c r="B17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.45" customHeight="1">
       <c r="B18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H18" s="7">
         <v>1732699990</v>
@@ -7284,22 +7270,22 @@
     </row>
     <row r="19" spans="2:8" ht="14.45" customHeight="1">
       <c r="B19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="H19" s="4">
         <v>17991385400</v>
@@ -7307,22 +7293,22 @@
     </row>
     <row r="20" spans="2:8" ht="14.45" customHeight="1">
       <c r="B20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="H20" s="7">
         <v>17992731001</v>
@@ -7330,68 +7316,68 @@
     </row>
     <row r="21" spans="2:8" ht="14.45" customHeight="1">
       <c r="B21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="14.45" customHeight="1">
       <c r="B22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="14.45" customHeight="1">
       <c r="B23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H23" s="4">
         <v>17991019999</v>
@@ -7399,68 +7385,68 @@
     </row>
     <row r="24" spans="2:8" ht="14.45" customHeight="1">
       <c r="B24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14.45" customHeight="1">
       <c r="B25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="14.45" customHeight="1">
       <c r="B26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="H26" s="7">
         <v>17996487770</v>
@@ -7468,22 +7454,22 @@
     </row>
     <row r="27" spans="2:8" ht="14.45" customHeight="1">
       <c r="B27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="H27" s="4">
         <v>17991436228</v>
@@ -7491,45 +7477,45 @@
     </row>
     <row r="28" spans="2:8" ht="14.45" customHeight="1">
       <c r="B28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="14.45" customHeight="1">
       <c r="B29" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H29" s="4">
         <v>17981671066</v>
@@ -7537,22 +7523,22 @@
     </row>
     <row r="30" spans="2:8" ht="14.45" customHeight="1">
       <c r="B30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="H30" s="7">
         <v>17997685797</v>
@@ -7560,45 +7546,45 @@
     </row>
     <row r="31" spans="2:8" ht="14.45" customHeight="1">
       <c r="B31" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G31" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="14.45" customHeight="1">
       <c r="B32" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H32" s="7">
         <v>17996369299</v>
@@ -7606,22 +7592,22 @@
     </row>
     <row r="33" spans="2:8" ht="14.45" customHeight="1">
       <c r="B33" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="H33" s="4">
         <v>17992296835</v>
@@ -7629,22 +7615,22 @@
     </row>
     <row r="34" spans="2:8" ht="14.45" customHeight="1">
       <c r="B34" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H34" s="7">
         <v>17997762047</v>
@@ -7652,22 +7638,22 @@
     </row>
     <row r="35" spans="2:8" ht="14.45" customHeight="1">
       <c r="B35" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H35" s="4">
         <v>17988298392</v>
@@ -7675,22 +7661,22 @@
     </row>
     <row r="36" spans="2:8" ht="14.45" customHeight="1">
       <c r="B36" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H36" s="7">
         <v>17988082952</v>
@@ -7698,22 +7684,22 @@
     </row>
     <row r="37" spans="2:8" ht="14.45" customHeight="1">
       <c r="B37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H37" s="4">
         <v>17996170113</v>
@@ -7721,22 +7707,22 @@
     </row>
     <row r="38" spans="2:8" ht="14.45" customHeight="1">
       <c r="B38" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H38" s="7">
         <v>17991133571</v>
@@ -7744,22 +7730,22 @@
     </row>
     <row r="39" spans="2:8" ht="14.45" customHeight="1">
       <c r="B39" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H39" s="4">
         <v>17997196510</v>
@@ -7767,45 +7753,45 @@
     </row>
     <row r="40" spans="2:8" ht="14.45" customHeight="1">
       <c r="B40" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.45" customHeight="1">
       <c r="B41" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H41" s="4">
         <v>17997212303</v>
@@ -7813,45 +7799,45 @@
     </row>
     <row r="42" spans="2:8" ht="14.45" customHeight="1">
       <c r="B42" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G42" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.45" customHeight="1">
       <c r="B43" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="H43" s="4">
         <v>17981170059</v>
@@ -7859,45 +7845,45 @@
     </row>
     <row r="44" spans="2:8" ht="14.45" customHeight="1">
       <c r="B44" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.45" customHeight="1">
       <c r="B45" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H45" s="4">
         <v>17996015188</v>
@@ -7905,68 +7891,68 @@
     </row>
     <row r="46" spans="2:8" ht="14.45" customHeight="1">
       <c r="B46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G46" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.45" customHeight="1">
       <c r="B47" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.45" customHeight="1">
       <c r="B48" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="H48" s="7">
         <v>17992170608</v>
@@ -7974,91 +7960,91 @@
     </row>
     <row r="49" spans="2:8" ht="14.45" customHeight="1">
       <c r="B49" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="14.45" customHeight="1">
       <c r="B50" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="14.45" customHeight="1">
       <c r="B51" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G51" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="14.45" customHeight="1">
       <c r="B52" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H52" s="7">
         <v>1732818196</v>
@@ -8066,137 +8052,137 @@
     </row>
     <row r="53" spans="2:8" ht="14.45" customHeight="1">
       <c r="B53" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G53" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="H53" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="14.45" customHeight="1">
       <c r="B54" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="14.45" customHeight="1">
       <c r="B55" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="14.45" customHeight="1">
       <c r="B56" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G56" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H56" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="14.45" customHeight="1">
       <c r="B57" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D57" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G57" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="14.45" customHeight="1">
       <c r="B58" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H58" s="7">
         <v>17997283279</v>
@@ -8204,91 +8190,91 @@
     </row>
     <row r="59" spans="2:8" ht="14.45" customHeight="1">
       <c r="B59" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G59" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="14.45" customHeight="1">
       <c r="B60" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G60" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="14.45" customHeight="1">
       <c r="B61" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G61" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="H61" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="14.45" customHeight="1">
       <c r="B62" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H62" s="7">
         <v>17997110972</v>
@@ -8296,68 +8282,68 @@
     </row>
     <row r="63" spans="2:8" ht="14.45" customHeight="1">
       <c r="B63" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="E63" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="14.45" customHeight="1">
       <c r="B64" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G64" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="14.45" customHeight="1">
       <c r="B65" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="G65" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="H65" s="4">
         <v>1732351010</v>
@@ -8365,137 +8351,137 @@
     </row>
     <row r="66" spans="2:8" ht="14.45" customHeight="1">
       <c r="B66" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>336</v>
-      </c>
       <c r="D66" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>337</v>
+        <v>319</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>648</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="14.45" customHeight="1">
       <c r="B67" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="F67" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="G67" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="14.45" customHeight="1">
       <c r="B68" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="14.45" customHeight="1">
       <c r="B69" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="G69" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="H69" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="14.45" customHeight="1">
       <c r="B70" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="G71" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>364</v>
       </c>
       <c r="H71" s="4">
         <v>17997727089</v>
@@ -8503,206 +8489,206 @@
     </row>
     <row r="72" spans="2:8" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>372</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="74" spans="2:8" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="75" spans="2:8" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="G76" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="G77" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="78" spans="2:8" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="G78" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="79" spans="2:8" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="80" spans="2:8" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H80" s="7">
         <v>17991167827</v>
@@ -8710,137 +8696,137 @@
     </row>
     <row r="81" spans="2:8" ht="14.45" customHeight="1">
       <c r="B81" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="G81" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="14.45" customHeight="1">
       <c r="B82" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="14.45" customHeight="1">
       <c r="B83" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="14.45" customHeight="1">
       <c r="B84" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="G84" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="14.45" customHeight="1">
       <c r="B85" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="F85" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E85" s="3" t="s">
+      <c r="H85" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="14.45" customHeight="1">
       <c r="B86" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H86" s="7">
         <v>17996021994</v>
@@ -8848,22 +8834,22 @@
     </row>
     <row r="87" spans="2:8" ht="14.45" customHeight="1">
       <c r="B87" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="F87" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="H87" s="4">
         <v>17991251239</v>
@@ -8871,160 +8857,160 @@
     </row>
     <row r="88" spans="2:8" ht="14.45" customHeight="1">
       <c r="B88" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="14.45" customHeight="1">
       <c r="B89" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="G89" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="14.45" customHeight="1">
       <c r="B90" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="14.45" customHeight="1">
       <c r="B91" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="14.45" customHeight="1">
       <c r="B92" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="G92" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="14.45" customHeight="1">
       <c r="B93" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="14.45" customHeight="1">
       <c r="B94" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H94" s="7">
         <v>1732348032</v>
@@ -9032,22 +9018,22 @@
     </row>
     <row r="95" spans="2:8" ht="14.45" customHeight="1">
       <c r="B95" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H95" s="4">
         <v>17996684410</v>
@@ -9055,131 +9041,131 @@
     </row>
     <row r="96" spans="2:8" ht="14.45" customHeight="1">
       <c r="B96" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="14.45" customHeight="1">
       <c r="B97" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="F97" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="H97" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="14.45" customHeight="1">
       <c r="B98" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="14.45" customHeight="1">
       <c r="B99" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="14.45" customHeight="1">
       <c r="B100" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="14.45" customHeight="1">
       <c r="B101" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>11</v>
@@ -9212,22 +9198,22 @@
     </row>
     <row r="103" spans="2:8" ht="14.45" customHeight="1">
       <c r="B103" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>515</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H103" s="4">
         <v>17981532805</v>
@@ -9235,137 +9221,137 @@
     </row>
     <row r="104" spans="2:8" ht="14.45" customHeight="1">
       <c r="B104" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="14.45" customHeight="1">
       <c r="B105" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>525</v>
-      </c>
       <c r="G105" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="H105" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="14.45" customHeight="1">
       <c r="B106" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="14.45" customHeight="1">
       <c r="B107" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>533</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="14.45" customHeight="1">
       <c r="B108" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="D108" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E108" s="3" t="s">
+      <c r="G108" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="14.45" customHeight="1">
       <c r="B109" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E109" s="3" t="s">
+      <c r="G109" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>546</v>
       </c>
       <c r="H109" s="4">
         <v>17981692483</v>
@@ -9373,206 +9359,206 @@
     </row>
     <row r="110" spans="2:8" ht="14.45" customHeight="1">
       <c r="B110" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>66</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="14.45" customHeight="1">
       <c r="B111" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>554</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="14.45" customHeight="1">
       <c r="B112" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="14.45" customHeight="1">
       <c r="B113" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="14.45" customHeight="1">
       <c r="B114" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="F114" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E114" s="3" t="s">
+      <c r="G114" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>569</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="14.45" customHeight="1">
       <c r="B115" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>574</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="14.45" customHeight="1">
       <c r="B116" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="G116" s="14" t="s">
         <v>579</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="H116" s="14" t="s">
         <v>580</v>
-      </c>
-      <c r="G116" s="14" t="s">
-        <v>581</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="14.45" customHeight="1">
       <c r="B117" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="14.45" customHeight="1">
       <c r="B118" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H118" s="7">
         <v>1732247602</v>
@@ -9580,39 +9566,39 @@
     </row>
     <row r="119" spans="2:8" ht="14.45" customHeight="1">
       <c r="B119" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E119" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>593</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="14.45" customHeight="1">
       <c r="B120" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>17</v>
@@ -9622,207 +9608,207 @@
     </row>
     <row r="121" spans="2:8" ht="14.45" customHeight="1">
       <c r="B121" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="14.45" customHeight="1">
       <c r="B122" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>66</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.45" customHeight="1">
       <c r="B123" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="E123" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="14.45" customHeight="1">
       <c r="B124" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>617</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>66</v>
       </c>
       <c r="G124" s="15"/>
       <c r="H124" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="14.45" customHeight="1">
       <c r="B125" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>621</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="14.45" customHeight="1">
       <c r="B126" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="14.45" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>629</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>631</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="14.45" customHeight="1">
       <c r="B128" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>637</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="14.45" customHeight="1">
       <c r="B129" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="D129" s="4" t="s">
+      <c r="F129" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G129" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="E129" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>638</v>
-      </c>
       <c r="H129" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="14.45" customHeight="1"/>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872CE246-BD3C-419F-8B24-299F573CBDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3937B422-DABA-417C-A65F-AFDD45ECACEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8520" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -6359,9 +6359,6 @@
     <t>CELULAR</t>
   </si>
   <si>
-    <t>Avenida Mirassolândia 1950 - Jardim Ana Celia</t>
-  </si>
-  <si>
     <t>Toda segunda 5ª feira do</t>
   </si>
   <si>
@@ -6380,6 +6377,9 @@
       </rPr>
       <t xml:space="preserve"> - Centro Mirassolândia</t>
     </r>
+  </si>
+  <si>
+    <t>Avenida Mirassolândia 1950 - Cep: 15045000 -Jardim Ana Celia</t>
   </si>
 </sst>
 </file>
@@ -7220,7 +7220,7 @@
         <v>86</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>87</v>
@@ -7769,7 +7769,7 @@
         <v>200</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>145</v>
@@ -8367,7 +8367,7 @@
         <v>318</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>17</v>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3937B422-DABA-417C-A65F-AFDD45ECACEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797154B6-8D64-403F-8EB6-CA2D7B3D91D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8520" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -6379,7 +6379,7 @@
     </r>
   </si>
   <si>
-    <t>Avenida Mirassolândia 1950 - Cep: 15045000 -Jardim Ana Celia</t>
+    <t>cep 15045000 Avenida Mirassolândia 1950 Jardim Ana Celia</t>
   </si>
 </sst>
 </file>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797154B6-8D64-403F-8EB6-CA2D7B3D91D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E22DE6-4748-4458-9539-E6ADBA00EAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8520" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -6379,7 +6379,7 @@
     </r>
   </si>
   <si>
-    <t>cep 15045000 Avenida Mirassolândia 1950 Jardim Ana Celia</t>
+    <t xml:space="preserve"> Rua Nagib Abissamura, 1665 Jardim Ana Celia</t>
   </si>
 </sst>
 </file>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E22DE6-4748-4458-9539-E6ADBA00EAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F293F4-1FF6-4B24-BA0C-C53295F56DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="2730" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="652">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -6380,6 +6380,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Rua Nagib Abissamura, 1665 Jardim Ana Celia</t>
+  </si>
+  <si>
+    <t>R. Nagib Abissamira - Res. Ana Célia, São José do Rio Preto - SP, 15045-500</t>
+  </si>
+  <si>
+    <t>NOME GOOGLE MAPS</t>
   </si>
 </sst>
 </file>
@@ -6847,7 +6853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4002065-77F3-44D2-ACFF-818DBCD21AC8}">
-  <dimension ref="B1:H130"/>
+  <dimension ref="B1:I130"/>
   <sheetFormatPr defaultColWidth="42.5703125" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="6" customWidth="1"/>
@@ -6858,10 +6864,11 @@
     <col min="6" max="6" width="37.140625" style="16" customWidth="1"/>
     <col min="7" max="7" width="22.5703125" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="42.5703125" style="6"/>
+    <col min="9" max="9" width="105" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="42.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="2:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
         <v>640</v>
       </c>
@@ -6883,8 +6890,11 @@
       <c r="H1" s="1" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="2" spans="2:8" ht="14.45" customHeight="1">
+      <c r="I1" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="14.45" customHeight="1">
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
@@ -6907,7 +6917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="14.45" customHeight="1">
+    <row r="3" spans="2:9" ht="14.45" customHeight="1">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -6930,7 +6940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14.45" customHeight="1">
+    <row r="4" spans="2:9" ht="14.45" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -6953,7 +6963,7 @@
         <v>17991739729</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14.45" customHeight="1">
+    <row r="5" spans="2:9" ht="14.45" customHeight="1">
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
@@ -6976,7 +6986,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14.45" customHeight="1">
+    <row r="6" spans="2:9" ht="14.45" customHeight="1">
       <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
@@ -6999,7 +7009,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14.45" customHeight="1">
+    <row r="7" spans="2:9" ht="14.45" customHeight="1">
       <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
@@ -7022,7 +7032,7 @@
         <v>17996164007</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14.45" customHeight="1">
+    <row r="8" spans="2:9" ht="14.45" customHeight="1">
       <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
@@ -7045,7 +7055,7 @@
         <v>17992105513</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="14.45" customHeight="1">
+    <row r="9" spans="2:9" ht="14.45" customHeight="1">
       <c r="B9" s="3" t="s">
         <v>47</v>
       </c>
@@ -7068,7 +7078,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14.45" customHeight="1">
+    <row r="10" spans="2:9" ht="14.45" customHeight="1">
       <c r="B10" s="3" t="s">
         <v>52</v>
       </c>
@@ -7091,7 +7101,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14.45" customHeight="1">
+    <row r="11" spans="2:9" ht="14.45" customHeight="1">
       <c r="B11" s="3" t="s">
         <v>58</v>
       </c>
@@ -7114,7 +7124,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="14.45" customHeight="1">
+    <row r="12" spans="2:9" ht="14.45" customHeight="1">
       <c r="B12" s="3" t="s">
         <v>64</v>
       </c>
@@ -7137,7 +7147,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14.45" customHeight="1">
+    <row r="13" spans="2:9" ht="14.45" customHeight="1">
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
@@ -7160,7 +7170,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14.45" customHeight="1">
+    <row r="14" spans="2:9" ht="14.45" customHeight="1">
       <c r="B14" s="3" t="s">
         <v>72</v>
       </c>
@@ -7183,7 +7193,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14.45" customHeight="1">
+    <row r="15" spans="2:9" ht="14.45" customHeight="1">
       <c r="B15" s="3" t="s">
         <v>78</v>
       </c>
@@ -7206,7 +7216,7 @@
         <v>17996707811</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14.45" customHeight="1">
+    <row r="16" spans="2:9" ht="14.45" customHeight="1">
       <c r="B16" s="3" t="s">
         <v>84</v>
       </c>
@@ -8333,7 +8343,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="14.45" customHeight="1">
+    <row r="65" spans="2:9" ht="14.45" customHeight="1">
       <c r="B65" s="3" t="s">
         <v>328</v>
       </c>
@@ -8356,7 +8366,7 @@
         <v>1732351010</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="14.45" customHeight="1">
+    <row r="66" spans="2:9" ht="14.45" customHeight="1">
       <c r="B66" s="3" t="s">
         <v>333</v>
       </c>
@@ -8378,8 +8388,11 @@
       <c r="H66" s="4" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="67" spans="2:8" ht="14.45" customHeight="1">
+      <c r="I66" s="6" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" ht="14.45" customHeight="1">
       <c r="B67" s="3" t="s">
         <v>337</v>
       </c>
@@ -8402,7 +8415,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="14.45" customHeight="1">
+    <row r="68" spans="2:9" ht="14.45" customHeight="1">
       <c r="B68" s="3" t="s">
         <v>343</v>
       </c>
@@ -8425,7 +8438,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="14.45" customHeight="1">
+    <row r="69" spans="2:9" ht="14.45" customHeight="1">
       <c r="B69" s="3" t="s">
         <v>347</v>
       </c>
@@ -8448,7 +8461,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="70" spans="2:8" ht="14.45" customHeight="1">
+    <row r="70" spans="2:9" ht="14.45" customHeight="1">
       <c r="B70" s="3" t="s">
         <v>353</v>
       </c>
@@ -8471,7 +8484,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="14.45" customHeight="1">
+    <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
         <v>358</v>
       </c>
@@ -8494,7 +8507,7 @@
         <v>17997727089</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="14.45" customHeight="1">
+    <row r="72" spans="2:9" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
         <v>362</v>
       </c>
@@ -8517,7 +8530,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="14.45" customHeight="1">
+    <row r="73" spans="2:9" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
         <v>367</v>
       </c>
@@ -8540,7 +8553,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="14.45" customHeight="1">
+    <row r="74" spans="2:9" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
         <v>372</v>
       </c>
@@ -8563,7 +8576,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="14.45" customHeight="1">
+    <row r="75" spans="2:9" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
         <v>377</v>
       </c>
@@ -8586,7 +8599,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="14.45" customHeight="1">
+    <row r="76" spans="2:9" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
         <v>382</v>
       </c>
@@ -8609,7 +8622,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="14.45" customHeight="1">
+    <row r="77" spans="2:9" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
         <v>388</v>
       </c>
@@ -8632,7 +8645,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="78" spans="2:8" ht="14.45" customHeight="1">
+    <row r="78" spans="2:9" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
         <v>394</v>
       </c>
@@ -8655,7 +8668,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="14.45" customHeight="1">
+    <row r="79" spans="2:9" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
         <v>400</v>
       </c>
@@ -8678,7 +8691,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="14.45" customHeight="1">
+    <row r="80" spans="2:9" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
         <v>405</v>
       </c>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F293F4-1FF6-4B24-BA0C-C53295F56DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A4AC0E-1450-41E2-BD73-7B8B43DC04BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="651">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Razão Social Centro Espírita</t>
   </si>
   <si>
-    <t>Cidade do Centro Espírita</t>
-  </si>
-  <si>
     <t>Endereço do Centro Espírita</t>
   </si>
   <si>
@@ -3165,16 +3162,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>S.J.Rio Preto</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Av. Faiez Nametalah Tarraf 1180 – Cidade Jardim</t>
     </r>
   </si>
@@ -6386,6 +6373,9 @@
   </si>
   <si>
     <t>NOME GOOGLE MAPS</t>
+  </si>
+  <si>
+    <t>São José do Rio Preto-SP</t>
   </si>
 </sst>
 </file>
@@ -6858,7 +6848,7 @@
   <cols>
     <col min="1" max="1" width="12.42578125" style="6" customWidth="1"/>
     <col min="2" max="2" width="37.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="42.5703125" style="6"/>
+    <col min="3" max="3" width="39.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="36.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61.140625" style="6" customWidth="1"/>
     <col min="6" max="6" width="37.140625" style="16" customWidth="1"/>
@@ -6870,94 +6860,94 @@
   <sheetData>
     <row r="1" spans="2:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="14.45" customHeight="1">
       <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14.45" customHeight="1">
       <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.45" customHeight="1">
       <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="H4" s="7">
         <v>17991739729</v>
@@ -6965,68 +6955,68 @@
     </row>
     <row r="5" spans="2:9" ht="14.45" customHeight="1">
       <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="14.45" customHeight="1">
       <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="14.45" customHeight="1">
       <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="H7" s="4">
         <v>17996164007</v>
@@ -7034,22 +7024,22 @@
     </row>
     <row r="8" spans="2:9" ht="14.45" customHeight="1">
       <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="H8" s="7">
         <v>17992105513</v>
@@ -7057,160 +7047,160 @@
     </row>
     <row r="9" spans="2:9" ht="14.45" customHeight="1">
       <c r="B9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="14.45" customHeight="1">
       <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="14.45" customHeight="1">
       <c r="B11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="14.45" customHeight="1">
       <c r="B12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="G12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="14.45" customHeight="1">
       <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="14.45" customHeight="1">
       <c r="B14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="14.45" customHeight="1">
       <c r="B15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="H15" s="4">
         <v>17996707811</v>
@@ -7218,22 +7208,22 @@
     </row>
     <row r="16" spans="2:9" ht="14.45" customHeight="1">
       <c r="B16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="H16" s="7">
         <v>17981625858</v>
@@ -7241,45 +7231,45 @@
     </row>
     <row r="17" spans="2:8" ht="14.45" customHeight="1">
       <c r="B17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.45" customHeight="1">
       <c r="B18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="H18" s="7">
         <v>1732699990</v>
@@ -7287,22 +7277,22 @@
     </row>
     <row r="19" spans="2:8" ht="14.45" customHeight="1">
       <c r="B19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="H19" s="4">
         <v>17991385400</v>
@@ -7310,22 +7300,22 @@
     </row>
     <row r="20" spans="2:8" ht="14.45" customHeight="1">
       <c r="B20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="H20" s="7">
         <v>17992731001</v>
@@ -7333,68 +7323,68 @@
     </row>
     <row r="21" spans="2:8" ht="14.45" customHeight="1">
       <c r="B21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="14.45" customHeight="1">
       <c r="B22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="14.45" customHeight="1">
       <c r="B23" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="H23" s="4">
         <v>17991019999</v>
@@ -7402,68 +7392,68 @@
     </row>
     <row r="24" spans="2:8" ht="14.45" customHeight="1">
       <c r="B24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="H24" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14.45" customHeight="1">
       <c r="B25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="14.45" customHeight="1">
       <c r="B26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="H26" s="7">
         <v>17996487770</v>
@@ -7471,22 +7461,22 @@
     </row>
     <row r="27" spans="2:8" ht="14.45" customHeight="1">
       <c r="B27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="H27" s="4">
         <v>17991436228</v>
@@ -7494,45 +7484,45 @@
     </row>
     <row r="28" spans="2:8" ht="14.45" customHeight="1">
       <c r="B28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="14.45" customHeight="1">
       <c r="B29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="H29" s="4">
         <v>17981671066</v>
@@ -7540,22 +7530,22 @@
     </row>
     <row r="30" spans="2:8" ht="14.45" customHeight="1">
       <c r="B30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="H30" s="7">
         <v>17997685797</v>
@@ -7563,45 +7553,45 @@
     </row>
     <row r="31" spans="2:8" ht="14.45" customHeight="1">
       <c r="B31" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="14.45" customHeight="1">
       <c r="B32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="H32" s="7">
         <v>17996369299</v>
@@ -7609,22 +7599,22 @@
     </row>
     <row r="33" spans="2:8" ht="14.45" customHeight="1">
       <c r="B33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="H33" s="4">
         <v>17992296835</v>
@@ -7632,22 +7622,22 @@
     </row>
     <row r="34" spans="2:8" ht="14.45" customHeight="1">
       <c r="B34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="H34" s="7">
         <v>17997762047</v>
@@ -7655,22 +7645,22 @@
     </row>
     <row r="35" spans="2:8" ht="14.45" customHeight="1">
       <c r="B35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="H35" s="4">
         <v>17988298392</v>
@@ -7678,22 +7668,22 @@
     </row>
     <row r="36" spans="2:8" ht="14.45" customHeight="1">
       <c r="B36" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="H36" s="7">
         <v>17988082952</v>
@@ -7701,22 +7691,22 @@
     </row>
     <row r="37" spans="2:8" ht="14.45" customHeight="1">
       <c r="B37" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="H37" s="4">
         <v>17996170113</v>
@@ -7724,22 +7714,22 @@
     </row>
     <row r="38" spans="2:8" ht="14.45" customHeight="1">
       <c r="B38" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="H38" s="7">
         <v>17991133571</v>
@@ -7747,22 +7737,22 @@
     </row>
     <row r="39" spans="2:8" ht="14.45" customHeight="1">
       <c r="B39" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H39" s="4">
         <v>17997196510</v>
@@ -7770,45 +7760,45 @@
     </row>
     <row r="40" spans="2:8" ht="14.45" customHeight="1">
       <c r="B40" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.45" customHeight="1">
       <c r="B41" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="H41" s="4">
         <v>17997212303</v>
@@ -7816,45 +7806,45 @@
     </row>
     <row r="42" spans="2:8" ht="14.45" customHeight="1">
       <c r="B42" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.45" customHeight="1">
       <c r="B43" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="H43" s="4">
         <v>17981170059</v>
@@ -7862,45 +7852,45 @@
     </row>
     <row r="44" spans="2:8" ht="14.45" customHeight="1">
       <c r="B44" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.45" customHeight="1">
       <c r="B45" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="H45" s="4">
         <v>17996015188</v>
@@ -7908,68 +7898,68 @@
     </row>
     <row r="46" spans="2:8" ht="14.45" customHeight="1">
       <c r="B46" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G46" s="4" t="s">
+      <c r="H46" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.45" customHeight="1">
       <c r="B47" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.45" customHeight="1">
       <c r="B48" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="H48" s="7">
         <v>17992170608</v>
@@ -7977,91 +7967,91 @@
     </row>
     <row r="49" spans="2:8" ht="14.45" customHeight="1">
       <c r="B49" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="E49" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="14.45" customHeight="1">
       <c r="B50" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E50" s="3" t="s">
+      <c r="F50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="4" t="s">
+      <c r="H50" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="14.45" customHeight="1">
       <c r="B51" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E51" s="3" t="s">
+      <c r="F51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" s="4" t="s">
+      <c r="H51" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="14.45" customHeight="1">
       <c r="B52" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="F52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="H52" s="7">
         <v>1732818196</v>
@@ -8069,137 +8059,137 @@
     </row>
     <row r="53" spans="2:8" ht="14.45" customHeight="1">
       <c r="B53" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="4" t="s">
+      <c r="H53" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="14.45" customHeight="1">
       <c r="B54" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="14.45" customHeight="1">
       <c r="B55" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="14.45" customHeight="1">
       <c r="B56" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="F56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G56" s="4" t="s">
+      <c r="H56" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="14.45" customHeight="1">
       <c r="B57" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G57" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="14.45" customHeight="1">
       <c r="B58" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="H58" s="7">
         <v>17997283279</v>
@@ -8207,91 +8197,91 @@
     </row>
     <row r="59" spans="2:8" ht="14.45" customHeight="1">
       <c r="B59" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" s="4" t="s">
+      <c r="H59" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="14.45" customHeight="1">
       <c r="B60" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G60" s="4" t="s">
+      <c r="H60" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="14.45" customHeight="1">
       <c r="B61" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="F61" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G61" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="14.45" customHeight="1">
       <c r="B62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="H62" s="7">
         <v>17997110972</v>
@@ -8299,68 +8289,68 @@
     </row>
     <row r="63" spans="2:8" ht="14.45" customHeight="1">
       <c r="B63" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="G63" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="14.45" customHeight="1">
       <c r="B64" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="F64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E64" s="3" t="s">
+      <c r="H64" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="14.45" customHeight="1">
       <c r="B65" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="F65" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E65" s="3" t="s">
+      <c r="G65" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="H65" s="4">
         <v>1732351010</v>
@@ -8368,140 +8358,140 @@
     </row>
     <row r="66" spans="2:9" ht="14.45" customHeight="1">
       <c r="B66" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="H66" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>336</v>
-      </c>
       <c r="I66" s="6" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="14.45" customHeight="1">
       <c r="B67" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="F67" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="G67" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="14.45" customHeight="1">
       <c r="B68" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="F68" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="69" spans="2:9" ht="14.45" customHeight="1">
       <c r="B69" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="G69" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="H69" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
       <c r="B70" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="F70" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E70" s="3" t="s">
+      <c r="H70" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="G71" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="H71" s="4">
         <v>17997727089</v>
@@ -8509,206 +8499,206 @@
     </row>
     <row r="72" spans="2:9" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="F72" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E72" s="3" t="s">
+      <c r="H72" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="F73" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E73" s="3" t="s">
+      <c r="H73" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="F74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E74" s="3" t="s">
+      <c r="H74" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E75" s="3" t="s">
+      <c r="H75" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="G76" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="G77" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="G78" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="F79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="D79" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E79" s="3" t="s">
+      <c r="H79" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="F80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="H80" s="7">
         <v>17991167827</v>
@@ -8716,137 +8706,137 @@
     </row>
     <row r="81" spans="2:8" ht="14.45" customHeight="1">
       <c r="B81" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="G81" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="14.45" customHeight="1">
       <c r="B82" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="F82" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E82" s="3" t="s">
+      <c r="H82" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="14.45" customHeight="1">
       <c r="B83" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="F83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E83" s="3" t="s">
+      <c r="H83" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="14.45" customHeight="1">
       <c r="B84" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="G84" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="14.45" customHeight="1">
       <c r="B85" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="F85" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E85" s="3" t="s">
+      <c r="H85" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="14.45" customHeight="1">
       <c r="B86" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="H86" s="7">
         <v>17996021994</v>
@@ -8854,22 +8844,22 @@
     </row>
     <row r="87" spans="2:8" ht="14.45" customHeight="1">
       <c r="B87" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="F87" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="H87" s="4">
         <v>17991251239</v>
@@ -8877,160 +8867,160 @@
     </row>
     <row r="88" spans="2:8" ht="14.45" customHeight="1">
       <c r="B88" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="F88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E88" s="3" t="s">
+      <c r="H88" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="14.45" customHeight="1">
       <c r="B89" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="G89" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="14.45" customHeight="1">
       <c r="B90" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="F90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D90" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E90" s="3" t="s">
+      <c r="H90" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="14.45" customHeight="1">
       <c r="B91" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="F91" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E91" s="3" t="s">
+      <c r="H91" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="14.45" customHeight="1">
       <c r="B92" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="G92" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="14.45" customHeight="1">
       <c r="B93" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="F93" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E93" s="3" t="s">
+      <c r="H93" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="14.45" customHeight="1">
       <c r="B94" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="F94" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>478</v>
       </c>
       <c r="H94" s="7">
         <v>1732348032</v>
@@ -9038,22 +9028,22 @@
     </row>
     <row r="95" spans="2:8" ht="14.45" customHeight="1">
       <c r="B95" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>481</v>
-      </c>
       <c r="F95" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H95" s="4">
         <v>17996684410</v>
@@ -9061,134 +9051,134 @@
     </row>
     <row r="96" spans="2:8" ht="14.45" customHeight="1">
       <c r="B96" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="F96" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E96" s="3" t="s">
+      <c r="H96" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="14.45" customHeight="1">
       <c r="B97" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="F97" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="H97" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="14.45" customHeight="1">
       <c r="B98" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="F98" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="D98" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E98" s="3" t="s">
+      <c r="H98" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="14.45" customHeight="1">
       <c r="B99" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="F99" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E99" s="3" t="s">
+      <c r="H99" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="14.45" customHeight="1">
       <c r="B100" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="F100" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="D100" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E100" s="3" t="s">
+      <c r="H100" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="14.45" customHeight="1">
       <c r="B101" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>509</v>
-      </c>
       <c r="F101" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -9200,40 +9190,40 @@
       <c r="C102" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E102" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E102" s="13" t="s">
+      <c r="F102" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F102" s="12" t="s">
+      <c r="G102" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G102" s="12" t="s">
+      <c r="H102" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="H102" s="12" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="14.45" customHeight="1">
       <c r="B103" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="F103" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>513</v>
       </c>
       <c r="H103" s="4">
         <v>17981532805</v>
@@ -9241,137 +9231,137 @@
     </row>
     <row r="104" spans="2:8" ht="14.45" customHeight="1">
       <c r="B104" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="F104" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E104" s="3" t="s">
+      <c r="H104" s="4" t="s">
         <v>516</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="14.45" customHeight="1">
       <c r="B105" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>522</v>
-      </c>
       <c r="G105" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="14.45" customHeight="1">
       <c r="B106" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="F106" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G106" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="D106" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E106" s="3" t="s">
+      <c r="H106" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="14.45" customHeight="1">
       <c r="B107" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="F107" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E107" s="3" t="s">
+      <c r="H107" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="14.45" customHeight="1">
       <c r="B108" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D108" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E108" s="3" t="s">
+      <c r="G108" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="14.45" customHeight="1">
       <c r="B109" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E109" s="3" t="s">
+      <c r="G109" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>543</v>
       </c>
       <c r="H109" s="4">
         <v>17981692483</v>
@@ -9379,206 +9369,206 @@
     </row>
     <row r="110" spans="2:8" ht="14.45" customHeight="1">
       <c r="B110" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="F110" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G110" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E110" s="3" t="s">
+      <c r="H110" s="4" t="s">
         <v>546</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="14.45" customHeight="1">
       <c r="B111" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="F111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E111" s="3" t="s">
+      <c r="H111" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="14.45" customHeight="1">
       <c r="B112" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="F112" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E112" s="3" t="s">
+      <c r="H112" s="4" t="s">
         <v>556</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="14.45" customHeight="1">
       <c r="B113" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="H113" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="14.45" customHeight="1">
       <c r="B114" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="F114" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E114" s="3" t="s">
+      <c r="G114" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="14.45" customHeight="1">
       <c r="B115" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="F115" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="D115" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E115" s="3" t="s">
+      <c r="H115" s="4" t="s">
         <v>571</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="14.45" customHeight="1">
       <c r="B116" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="G116" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="H116" s="14" t="s">
         <v>577</v>
-      </c>
-      <c r="G116" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="14.45" customHeight="1">
       <c r="B117" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="F117" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>581</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="14.45" customHeight="1">
       <c r="B118" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="F118" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G118" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>587</v>
       </c>
       <c r="H118" s="7">
         <v>1732247602</v>
@@ -9586,249 +9576,249 @@
     </row>
     <row r="119" spans="2:8" ht="14.45" customHeight="1">
       <c r="B119" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E119" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="F119" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G119" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="D119" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E119" s="3" t="s">
+      <c r="H119" s="4" t="s">
         <v>590</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="14.45" customHeight="1">
       <c r="B120" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>318</v>
+        <v>591</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>650</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G120" s="15"/>
       <c r="H120" s="5"/>
     </row>
     <row r="121" spans="2:8" ht="14.45" customHeight="1">
       <c r="B121" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="F121" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="D121" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E121" s="3" t="s">
+      <c r="H121" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="14.45" customHeight="1">
       <c r="B122" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="F122" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G122" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="D122" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E122" s="3" t="s">
+      <c r="H122" s="4" t="s">
         <v>602</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.45" customHeight="1">
       <c r="B123" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="E123" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="F123" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G123" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="H123" s="4" t="s">
         <v>608</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="14.45" customHeight="1">
       <c r="B124" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="D124" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>614</v>
-      </c>
       <c r="F124" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G124" s="15"/>
       <c r="H124" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="14.45" customHeight="1">
       <c r="B125" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="F125" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G125" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="D125" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="E125" s="3" t="s">
+      <c r="H125" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="14.45" customHeight="1">
       <c r="B126" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="F126" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G126" s="15" t="s">
         <v>622</v>
       </c>
-      <c r="D126" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="E126" s="3" t="s">
+      <c r="H126" s="4" t="s">
         <v>623</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G126" s="15" t="s">
-        <v>624</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="14.45" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="F127" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="D127" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="E127" s="3" t="s">
+      <c r="H127" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="14.45" customHeight="1">
       <c r="B128" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="F128" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="H128" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="14.45" customHeight="1">
       <c r="B129" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="D129" s="4" t="s">
+      <c r="F129" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G129" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="E129" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>635</v>
-      </c>
       <c r="H129" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="14.45" customHeight="1"/>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A4AC0E-1450-41E2-BD73-7B8B43DC04BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F965C1-DE66-4384-81EF-4AC509AD62B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="652">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -3495,16 +3495,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Meimei (Schimidt)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Ass. Beneficente e Educ. Meimei</t>
     </r>
   </si>
@@ -6376,6 +6366,12 @@
   </si>
   <si>
     <t>São José do Rio Preto-SP</t>
+  </si>
+  <si>
+    <t>Meimei (Schimidt)</t>
+  </si>
+  <si>
+    <t>Schimidt</t>
   </si>
 </sst>
 </file>
@@ -6860,28 +6856,28 @@
   <sheetData>
     <row r="1" spans="2:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="14.45" customHeight="1">
@@ -7220,7 +7216,7 @@
         <v>85</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>86</v>
@@ -7769,7 +7765,7 @@
         <v>199</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>144</v>
@@ -8295,7 +8291,7 @@
         <v>316</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>317</v>
@@ -8318,7 +8314,7 @@
         <v>322</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>323</v>
@@ -8341,7 +8337,7 @@
         <v>327</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>328</v>
@@ -8364,10 +8360,10 @@
         <v>332</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>16</v>
@@ -8379,7 +8375,7 @@
         <v>334</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="14.45" customHeight="1">
@@ -8390,7 +8386,7 @@
         <v>336</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>337</v>
@@ -8413,7 +8409,7 @@
         <v>342</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>343</v>
@@ -8436,7 +8432,7 @@
         <v>346</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>347</v>
@@ -8452,46 +8448,46 @@
       </c>
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>353</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G70" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>228</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E71" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="H71" s="4">
         <v>17997727089</v>
@@ -8499,206 +8495,206 @@
     </row>
     <row r="72" spans="2:9" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G72" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>372</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G74" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G75" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="D77" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="G77" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H80" s="7">
         <v>17991167827</v>
@@ -8706,137 +8702,137 @@
     </row>
     <row r="81" spans="2:8" ht="14.45" customHeight="1">
       <c r="B81" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="14.45" customHeight="1">
       <c r="B82" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="14.45" customHeight="1">
       <c r="B83" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="14.45" customHeight="1">
       <c r="B84" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G84" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="14.45" customHeight="1">
       <c r="B85" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G85" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="H85" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="14.45" customHeight="1">
       <c r="B86" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H86" s="7">
         <v>17996021994</v>
@@ -8844,22 +8840,22 @@
     </row>
     <row r="87" spans="2:8" ht="14.45" customHeight="1">
       <c r="B87" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H87" s="4">
         <v>17991251239</v>
@@ -8867,160 +8863,160 @@
     </row>
     <row r="88" spans="2:8" ht="14.45" customHeight="1">
       <c r="B88" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="14.45" customHeight="1">
       <c r="B89" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="D89" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="G89" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="14.45" customHeight="1">
       <c r="B90" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="H90" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="14.45" customHeight="1">
       <c r="B91" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="D91" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="14.45" customHeight="1">
       <c r="B92" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="14.45" customHeight="1">
       <c r="B93" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="D93" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="14.45" customHeight="1">
       <c r="B94" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H94" s="7">
         <v>1732348032</v>
@@ -9028,16 +9024,16 @@
     </row>
     <row r="95" spans="2:8" ht="14.45" customHeight="1">
       <c r="B95" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>479</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>27</v>
@@ -9051,131 +9047,131 @@
     </row>
     <row r="96" spans="2:8" ht="14.45" customHeight="1">
       <c r="B96" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>482</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G96" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="H96" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="14.45" customHeight="1">
       <c r="B97" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D97" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="F97" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="G97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="14.45" customHeight="1">
       <c r="B98" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="D98" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G98" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="14.45" customHeight="1">
       <c r="B99" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G99" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="14.45" customHeight="1">
       <c r="B100" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="D100" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G100" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="H100" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="14.45" customHeight="1">
       <c r="B101" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>10</v>
@@ -9191,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>2</v>
@@ -9208,22 +9204,22 @@
     </row>
     <row r="103" spans="2:8" ht="14.45" customHeight="1">
       <c r="B103" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H103" s="4">
         <v>17981532805</v>
@@ -9231,42 +9227,42 @@
     </row>
     <row r="104" spans="2:8" ht="14.45" customHeight="1">
       <c r="B104" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="D104" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G104" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="14.45" customHeight="1">
       <c r="B105" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="D105" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>520</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>324</v>
@@ -9277,91 +9273,91 @@
     </row>
     <row r="106" spans="2:8" ht="14.45" customHeight="1">
       <c r="B106" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="D106" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G106" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="H106" s="4" t="s">
         <v>524</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="14.45" customHeight="1">
       <c r="B107" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G107" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="H107" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="14.45" customHeight="1">
       <c r="B108" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="D108" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="G108" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>535</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="14.45" customHeight="1">
       <c r="B109" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="D109" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="D109" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="G109" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="H109" s="4">
         <v>17981692483</v>
@@ -9369,177 +9365,177 @@
     </row>
     <row r="110" spans="2:8" ht="14.45" customHeight="1">
       <c r="B110" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="D110" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G110" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>545</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="14.45" customHeight="1">
       <c r="B111" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="D111" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="14.45" customHeight="1">
       <c r="B112" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>554</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G112" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>555</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="14.45" customHeight="1">
       <c r="B113" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>558</v>
-      </c>
       <c r="D113" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G113" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="H113" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="14.45" customHeight="1">
       <c r="B114" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="D114" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="D114" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E114" s="3" t="s">
+      <c r="F114" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="G114" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="14.45" customHeight="1">
       <c r="B115" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G115" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="14.45" customHeight="1">
       <c r="B116" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="D116" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="G116" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="G116" s="14" t="s">
+      <c r="H116" s="14" t="s">
         <v>576</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="14.45" customHeight="1">
       <c r="B117" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="D117" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>580</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>10</v>
@@ -9548,27 +9544,27 @@
         <v>127</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="14.45" customHeight="1">
       <c r="B118" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H118" s="7">
         <v>1732247602</v>
@@ -9576,25 +9572,25 @@
     </row>
     <row r="119" spans="2:8" ht="14.45" customHeight="1">
       <c r="B119" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E119" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G119" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="14.45" customHeight="1">
@@ -9602,13 +9598,13 @@
         <v>123</v>
       </c>
       <c r="C120" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>16</v>
@@ -9618,207 +9614,207 @@
     </row>
     <row r="121" spans="2:8" ht="14.45" customHeight="1">
       <c r="B121" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>594</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>595</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G121" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="14.45" customHeight="1">
       <c r="B122" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G122" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>601</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.45" customHeight="1">
       <c r="B123" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E123" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G123" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>607</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="14.45" customHeight="1">
       <c r="B124" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="E124" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>612</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G124" s="15"/>
       <c r="H124" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="14.45" customHeight="1">
       <c r="B125" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="D125" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>616</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="H125" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="14.45" customHeight="1">
       <c r="B126" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="D126" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>620</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>621</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G126" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="14.45" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G127" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>627</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="14.45" customHeight="1">
       <c r="B128" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="E128" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>632</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G128" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="H128" s="4" t="s">
         <v>633</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="14.45" customHeight="1">
       <c r="B129" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>636</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>637</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G129" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>633</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="14.45" customHeight="1"/>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F965C1-DE66-4384-81EF-4AC509AD62B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31391C1-9759-4484-9A76-2DD3CC617CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="8625" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -76,16 +76,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Ass. Esp. Benef. Francisco de Assis</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Bady Bassit</t>
     </r>
   </si>
@@ -1662,16 +1652,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Inst. Estudos Esp. Francisco de Assis</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Rua São Bento 2125 - Bairro São José</t>
     </r>
   </si>
@@ -3505,16 +3485,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Rua Izaltina de Oliveira Pandim, 15 - Santa Catarina – Distrito Eng. Schi</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Maria Cristina</t>
     </r>
   </si>
@@ -5349,16 +5319,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Ass.Esp.Benef. Maria de Nazareth</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Rua Ênio Poli, 357 - Jardim Jaguaré (J.Paulo II)</t>
     </r>
   </si>
@@ -6336,9 +6296,6 @@
     <t>CELULAR</t>
   </si>
   <si>
-    <t>Toda segunda 5ª feira do</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -6372,6 +6329,21 @@
   </si>
   <si>
     <t>Schimidt</t>
+  </si>
+  <si>
+    <t>Rua Izaltina de Oliveira Pandim, 15 - Santa Catarina – Distrito Engenheiro Schimidt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toda segunda 5ª feira </t>
+  </si>
+  <si>
+    <t>Ass. Espirita Benef. Francisco de Assis</t>
+  </si>
+  <si>
+    <t>Inst. Estudos Espirita Francisco de Assis</t>
+  </si>
+  <si>
+    <t>Ass.Espirita Benef. Maria de Nazareth</t>
   </si>
 </sst>
 </file>
@@ -6844,10 +6816,10 @@
   <cols>
     <col min="1" max="1" width="12.42578125" style="6" customWidth="1"/>
     <col min="2" max="2" width="37.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="48" style="6" customWidth="1"/>
     <col min="4" max="4" width="36.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="85" style="6" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" style="16" customWidth="1"/>
     <col min="7" max="7" width="22.5703125" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.140625" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="105" style="6" customWidth="1"/>
@@ -6856,94 +6828,94 @@
   <sheetData>
     <row r="1" spans="2:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="14.45" customHeight="1">
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14.45" customHeight="1">
       <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.45" customHeight="1">
       <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="H4" s="7">
         <v>17991739729</v>
@@ -6951,68 +6923,68 @@
     </row>
     <row r="5" spans="2:9" ht="14.45" customHeight="1">
       <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="14.45" customHeight="1">
       <c r="B6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="14.45" customHeight="1">
       <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="H7" s="4">
         <v>17996164007</v>
@@ -7020,22 +6992,22 @@
     </row>
     <row r="8" spans="2:9" ht="14.45" customHeight="1">
       <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="H8" s="7">
         <v>17992105513</v>
@@ -7043,160 +7015,160 @@
     </row>
     <row r="9" spans="2:9" ht="14.45" customHeight="1">
       <c r="B9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="14.45" customHeight="1">
       <c r="B10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="14.45" customHeight="1">
       <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="14.45" customHeight="1">
       <c r="B12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="G12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="14.45" customHeight="1">
       <c r="B13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="14.45" customHeight="1">
       <c r="B14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="14.45" customHeight="1">
       <c r="B15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="H15" s="4">
         <v>17996707811</v>
@@ -7204,22 +7176,22 @@
     </row>
     <row r="16" spans="2:9" ht="14.45" customHeight="1">
       <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="H16" s="7">
         <v>17981625858</v>
@@ -7227,45 +7199,45 @@
     </row>
     <row r="17" spans="2:8" ht="14.45" customHeight="1">
       <c r="B17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.45" customHeight="1">
       <c r="B18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="H18" s="7">
         <v>1732699990</v>
@@ -7273,22 +7245,22 @@
     </row>
     <row r="19" spans="2:8" ht="14.45" customHeight="1">
       <c r="B19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="H19" s="4">
         <v>17991385400</v>
@@ -7296,22 +7268,22 @@
     </row>
     <row r="20" spans="2:8" ht="14.45" customHeight="1">
       <c r="B20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="H20" s="7">
         <v>17992731001</v>
@@ -7319,68 +7291,68 @@
     </row>
     <row r="21" spans="2:8" ht="14.45" customHeight="1">
       <c r="B21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="14.45" customHeight="1">
       <c r="B22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="14.45" customHeight="1">
       <c r="B23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="H23" s="4">
         <v>17991019999</v>
@@ -7388,68 +7360,68 @@
     </row>
     <row r="24" spans="2:8" ht="14.45" customHeight="1">
       <c r="B24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="H24" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14.45" customHeight="1">
       <c r="B25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="14.45" customHeight="1">
       <c r="B26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="H26" s="7">
         <v>17996487770</v>
@@ -7457,22 +7429,22 @@
     </row>
     <row r="27" spans="2:8" ht="14.45" customHeight="1">
       <c r="B27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="H27" s="4">
         <v>17991436228</v>
@@ -7480,45 +7452,45 @@
     </row>
     <row r="28" spans="2:8" ht="14.45" customHeight="1">
       <c r="B28" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="14.45" customHeight="1">
       <c r="B29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="H29" s="4">
         <v>17981671066</v>
@@ -7526,22 +7498,22 @@
     </row>
     <row r="30" spans="2:8" ht="14.45" customHeight="1">
       <c r="B30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="H30" s="7">
         <v>17997685797</v>
@@ -7549,45 +7521,45 @@
     </row>
     <row r="31" spans="2:8" ht="14.45" customHeight="1">
       <c r="B31" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="14.45" customHeight="1">
       <c r="B32" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="F32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="H32" s="7">
         <v>17996369299</v>
@@ -7595,22 +7567,22 @@
     </row>
     <row r="33" spans="2:8" ht="14.45" customHeight="1">
       <c r="B33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="H33" s="4">
         <v>17992296835</v>
@@ -7618,22 +7590,22 @@
     </row>
     <row r="34" spans="2:8" ht="14.45" customHeight="1">
       <c r="B34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="F34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="H34" s="7">
         <v>17997762047</v>
@@ -7641,22 +7613,22 @@
     </row>
     <row r="35" spans="2:8" ht="14.45" customHeight="1">
       <c r="B35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="F35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="H35" s="4">
         <v>17988298392</v>
@@ -7664,22 +7636,22 @@
     </row>
     <row r="36" spans="2:8" ht="14.45" customHeight="1">
       <c r="B36" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="F36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="H36" s="7">
         <v>17988082952</v>
@@ -7687,22 +7659,22 @@
     </row>
     <row r="37" spans="2:8" ht="14.45" customHeight="1">
       <c r="B37" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="F37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="H37" s="4">
         <v>17996170113</v>
@@ -7710,22 +7682,22 @@
     </row>
     <row r="38" spans="2:8" ht="14.45" customHeight="1">
       <c r="B38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="F38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>192</v>
       </c>
       <c r="H38" s="7">
         <v>17991133571</v>
@@ -7733,22 +7705,22 @@
     </row>
     <row r="39" spans="2:8" ht="14.45" customHeight="1">
       <c r="B39" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="F39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="H39" s="4">
         <v>17997196510</v>
@@ -7756,45 +7728,45 @@
     </row>
     <row r="40" spans="2:8" ht="14.45" customHeight="1">
       <c r="B40" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.45" customHeight="1">
       <c r="B41" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="F41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>204</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="H41" s="4">
         <v>17997212303</v>
@@ -7802,45 +7774,45 @@
     </row>
     <row r="42" spans="2:8" ht="14.45" customHeight="1">
       <c r="B42" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E42" s="3" t="s">
+      <c r="H42" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.45" customHeight="1">
       <c r="B43" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="G43" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="H43" s="4">
         <v>17981170059</v>
@@ -7848,45 +7820,45 @@
     </row>
     <row r="44" spans="2:8" ht="14.45" customHeight="1">
       <c r="B44" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="F44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="H44" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.45" customHeight="1">
       <c r="B45" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="F45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="H45" s="4">
         <v>17996015188</v>
@@ -7894,68 +7866,68 @@
     </row>
     <row r="46" spans="2:8" ht="14.45" customHeight="1">
       <c r="B46" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="F46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="H46" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.45" customHeight="1">
       <c r="B47" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="G47" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.45" customHeight="1">
       <c r="B48" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="G48" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="H48" s="7">
         <v>17992170608</v>
@@ -7963,91 +7935,91 @@
     </row>
     <row r="49" spans="2:8" ht="14.45" customHeight="1">
       <c r="B49" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="F49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="14.45" customHeight="1">
       <c r="B50" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="F50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E50" s="3" t="s">
+      <c r="H50" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="14.45" customHeight="1">
       <c r="B51" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="F51" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E51" s="3" t="s">
+      <c r="H51" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="14.45" customHeight="1">
       <c r="B52" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="F52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="H52" s="7">
         <v>1732818196</v>
@@ -8055,137 +8027,137 @@
     </row>
     <row r="53" spans="2:8" ht="14.45" customHeight="1">
       <c r="B53" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="F53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="H53" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="14.45" customHeight="1">
       <c r="B54" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="H54" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="14.45" customHeight="1">
       <c r="B55" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="F55" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="G55" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="14.45" customHeight="1">
       <c r="B56" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="F56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="H56" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="14.45" customHeight="1">
       <c r="B57" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="F57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="H57" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="14.45" customHeight="1">
       <c r="B58" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="F58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="H58" s="7">
         <v>17997283279</v>
@@ -8193,91 +8165,91 @@
     </row>
     <row r="59" spans="2:8" ht="14.45" customHeight="1">
       <c r="B59" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="F59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="H59" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="14.45" customHeight="1">
       <c r="B60" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="F60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E60" s="3" t="s">
+      <c r="H60" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="14.45" customHeight="1">
       <c r="B61" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="F61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="H61" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="14.45" customHeight="1">
       <c r="B62" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="F62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="H62" s="7">
         <v>17997110972</v>
@@ -8285,68 +8257,68 @@
     </row>
     <row r="63" spans="2:8" ht="14.45" customHeight="1">
       <c r="B63" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="F63" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="G63" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="14.45" customHeight="1">
       <c r="B64" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="F64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="D64" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E64" s="3" t="s">
+      <c r="H64" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="14.45" customHeight="1">
       <c r="B65" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="F65" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E65" s="3" t="s">
+      <c r="G65" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="H65" s="4">
         <v>1732351010</v>
@@ -8354,140 +8326,140 @@
     </row>
     <row r="66" spans="2:9" ht="14.45" customHeight="1">
       <c r="B66" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="H66" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>334</v>
-      </c>
       <c r="I66" s="6" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="14.45" customHeight="1">
       <c r="B67" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="F67" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="G67" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="14.45" customHeight="1">
       <c r="B68" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="F68" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="69" spans="2:9" ht="14.45" customHeight="1">
       <c r="B69" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="G69" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="H69" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
       <c r="B70" s="8" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="H71" s="4">
         <v>17997727089</v>
@@ -8495,206 +8467,206 @@
     </row>
     <row r="72" spans="2:9" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="H72" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="H73" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="H74" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="H75" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="G76" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="H76" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="G77" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="H77" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="G78" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="H78" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="H79" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>405</v>
       </c>
       <c r="H80" s="7">
         <v>17991167827</v>
@@ -8702,137 +8674,137 @@
     </row>
     <row r="81" spans="2:8" ht="14.45" customHeight="1">
       <c r="B81" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="G81" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="H81" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="14.45" customHeight="1">
       <c r="B82" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="H82" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="14.45" customHeight="1">
       <c r="B83" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="H83" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="14.45" customHeight="1">
       <c r="B84" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="G84" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="H84" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="14.45" customHeight="1">
       <c r="B85" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="H85" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="14.45" customHeight="1">
       <c r="B86" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H86" s="7">
         <v>17996021994</v>
@@ -8840,22 +8812,22 @@
     </row>
     <row r="87" spans="2:8" ht="14.45" customHeight="1">
       <c r="B87" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="H87" s="4">
         <v>17991251239</v>
@@ -8863,160 +8835,160 @@
     </row>
     <row r="88" spans="2:8" ht="14.45" customHeight="1">
       <c r="B88" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="H88" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="14.45" customHeight="1">
       <c r="B89" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="G89" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D89" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="H89" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="14.45" customHeight="1">
       <c r="B90" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="H90" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="14.45" customHeight="1">
       <c r="B91" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="H91" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="14.45" customHeight="1">
       <c r="B92" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="G92" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="H92" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="14.45" customHeight="1">
       <c r="B93" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="H93" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="14.45" customHeight="1">
       <c r="B94" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="H94" s="7">
         <v>1732348032</v>
@@ -9024,22 +8996,22 @@
     </row>
     <row r="95" spans="2:8" ht="14.45" customHeight="1">
       <c r="B95" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H95" s="4">
         <v>17996684410</v>
@@ -9047,134 +9019,134 @@
     </row>
     <row r="96" spans="2:8" ht="14.45" customHeight="1">
       <c r="B96" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="H96" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="14.45" customHeight="1">
       <c r="B97" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="H97" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="14.45" customHeight="1">
       <c r="B98" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="H98" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="14.45" customHeight="1">
       <c r="B99" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="H99" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="14.45" customHeight="1">
       <c r="B100" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="H100" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="14.45" customHeight="1">
       <c r="B101" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -9187,7 +9159,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>2</v>
@@ -9204,22 +9176,22 @@
     </row>
     <row r="103" spans="2:8" ht="14.45" customHeight="1">
       <c r="B103" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G103" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="H103" s="4">
         <v>17981532805</v>
@@ -9227,137 +9199,137 @@
     </row>
     <row r="104" spans="2:8" ht="14.45" customHeight="1">
       <c r="B104" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="H104" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="14.45" customHeight="1">
       <c r="B105" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="F105" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>519</v>
-      </c>
       <c r="G105" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="14.45" customHeight="1">
       <c r="B106" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G106" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="H106" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="14.45" customHeight="1">
       <c r="B107" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G107" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="H107" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="14.45" customHeight="1">
       <c r="B108" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="F108" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="G108" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E108" s="3" t="s">
+      <c r="H108" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="14.45" customHeight="1">
       <c r="B109" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="G109" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>540</v>
       </c>
       <c r="H109" s="4">
         <v>17981692483</v>
@@ -9365,206 +9337,206 @@
     </row>
     <row r="110" spans="2:8" ht="14.45" customHeight="1">
       <c r="B110" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="14.45" customHeight="1">
       <c r="B111" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>546</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="14.45" customHeight="1">
       <c r="B112" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="14.45" customHeight="1">
       <c r="B113" s="3" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="14.45" customHeight="1">
       <c r="B114" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="H114" s="4" t="s">
         <v>561</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="14.45" customHeight="1">
       <c r="B115" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="14.45" customHeight="1">
       <c r="B116" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G116" s="14" t="s">
         <v>571</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="H116" s="14" t="s">
         <v>572</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="G116" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="14.45" customHeight="1">
       <c r="B117" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="14.45" customHeight="1">
       <c r="B118" s="3" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="H118" s="7">
         <v>1732247602</v>
@@ -9572,249 +9544,249 @@
     </row>
     <row r="119" spans="2:8" ht="14.45" customHeight="1">
       <c r="B119" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="14.45" customHeight="1">
       <c r="B120" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G120" s="15"/>
       <c r="H120" s="5"/>
     </row>
     <row r="121" spans="2:8" ht="14.45" customHeight="1">
       <c r="B121" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="14.45" customHeight="1">
       <c r="B122" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.45" customHeight="1">
       <c r="B123" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="H123" s="4" t="s">
         <v>603</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="14.45" customHeight="1">
       <c r="B124" s="3" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G124" s="15"/>
       <c r="H124" s="4" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="14.45" customHeight="1">
       <c r="B125" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="H125" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="14.45" customHeight="1">
       <c r="B126" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G126" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G126" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="14.45" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>623</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="14.45" customHeight="1">
       <c r="B128" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="H128" s="4" t="s">
         <v>629</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="14.45" customHeight="1">
       <c r="B129" s="3" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="14.45" customHeight="1"/>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31391C1-9759-4484-9A76-2DD3CC617CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD4D996-8FCF-4E7C-96E4-D918924B8E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8625" yWindow="165" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="11595" yWindow="345" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -3475,16 +3475,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Ass. Beneficente e Educ. Meimei</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Maria Cristina</t>
     </r>
   </si>
@@ -3705,16 +3695,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Ass.Esp.Ben.Caminho da Esperança</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Rua Clodulpho Sellamn Benevides 377</t>
     </r>
   </si>
@@ -6328,12 +6308,6 @@
     <t>Meimei (Schimidt)</t>
   </si>
   <si>
-    <t>Schimidt</t>
-  </si>
-  <si>
-    <t>Rua Izaltina de Oliveira Pandim, 15 - Santa Catarina – Distrito Engenheiro Schimidt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Toda segunda 5ª feira </t>
   </si>
   <si>
@@ -6344,6 +6318,18 @@
   </si>
   <si>
     <t>Ass.Espirita Benef. Maria de Nazareth</t>
+  </si>
+  <si>
+    <t>Schimidt-SP</t>
+  </si>
+  <si>
+    <t>Ass. Beneficente e Educacional Meimei - Abem</t>
+  </si>
+  <si>
+    <t>Ass.Esp.Ben.Caminho da Esperança</t>
+  </si>
+  <si>
+    <t>Rua Izaltina de Oliveira Pandim, 15 - Estancia Manacaz – Distrito Engenheiro Schimidt</t>
   </si>
 </sst>
 </file>
@@ -6816,7 +6802,7 @@
   <cols>
     <col min="1" max="1" width="12.42578125" style="6" customWidth="1"/>
     <col min="2" max="2" width="37.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="48" style="6" customWidth="1"/>
+    <col min="3" max="3" width="50.42578125" style="6" customWidth="1"/>
     <col min="4" max="4" width="36.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="85" style="6" customWidth="1"/>
     <col min="6" max="6" width="38.85546875" style="16" customWidth="1"/>
@@ -6828,28 +6814,28 @@
   <sheetData>
     <row r="1" spans="2:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="14.45" customHeight="1">
@@ -6857,7 +6843,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
@@ -7188,7 +7174,7 @@
         <v>84</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>85</v>
@@ -7547,7 +7533,7 @@
         <v>165</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>136</v>
@@ -7737,7 +7723,7 @@
         <v>197</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>143</v>
@@ -8263,7 +8249,7 @@
         <v>314</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>315</v>
@@ -8286,7 +8272,7 @@
         <v>320</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>321</v>
@@ -8309,7 +8295,7 @@
         <v>325</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>326</v>
@@ -8332,10 +8318,10 @@
         <v>330</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>15</v>
@@ -8347,7 +8333,7 @@
         <v>332</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="14.45" customHeight="1">
@@ -8358,7 +8344,7 @@
         <v>334</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>335</v>
@@ -8381,7 +8367,7 @@
         <v>340</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>341</v>
@@ -8404,7 +8390,7 @@
         <v>344</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>345</v>
@@ -8421,45 +8407,45 @@
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
       <c r="B70" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>349</v>
+        <v>643</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>649</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G70" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>226</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E71" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="H71" s="4">
         <v>17997727089</v>
@@ -8467,206 +8453,206 @@
     </row>
     <row r="72" spans="2:9" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G72" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>363</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G74" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="G76" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="G77" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="G78" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H80" s="7">
         <v>17991167827</v>
@@ -8674,137 +8660,137 @@
     </row>
     <row r="81" spans="2:8" ht="14.45" customHeight="1">
       <c r="B81" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="G81" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="14.45" customHeight="1">
       <c r="B82" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="14.45" customHeight="1">
       <c r="B83" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="14.45" customHeight="1">
       <c r="B84" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="G84" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="14.45" customHeight="1">
       <c r="B85" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>143</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="14.45" customHeight="1">
       <c r="B86" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H86" s="7">
         <v>17996021994</v>
@@ -8812,22 +8798,22 @@
     </row>
     <row r="87" spans="2:8" ht="14.45" customHeight="1">
       <c r="B87" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>143</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H87" s="4">
         <v>17991251239</v>
@@ -8835,160 +8821,160 @@
     </row>
     <row r="88" spans="2:8" ht="14.45" customHeight="1">
       <c r="B88" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="14.45" customHeight="1">
       <c r="B89" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D89" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="G89" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="14.45" customHeight="1">
       <c r="B90" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>450</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="14.45" customHeight="1">
       <c r="B91" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="14.45" customHeight="1">
       <c r="B92" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="G92" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="14.45" customHeight="1">
       <c r="B93" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>466</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="14.45" customHeight="1">
       <c r="B94" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H94" s="7">
         <v>1732348032</v>
@@ -8996,16 +8982,16 @@
     </row>
     <row r="95" spans="2:8" ht="14.45" customHeight="1">
       <c r="B95" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>26</v>
@@ -9019,131 +9005,131 @@
     </row>
     <row r="96" spans="2:8" ht="14.45" customHeight="1">
       <c r="B96" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="14.45" customHeight="1">
       <c r="B97" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="F97" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="D97" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="H97" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="14.45" customHeight="1">
       <c r="B98" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="14.45" customHeight="1">
       <c r="B99" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="14.45" customHeight="1">
       <c r="B100" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="14.45" customHeight="1">
       <c r="B101" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>503</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>9</v>
@@ -9159,7 +9145,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>2</v>
@@ -9176,22 +9162,22 @@
     </row>
     <row r="103" spans="2:8" ht="14.45" customHeight="1">
       <c r="B103" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H103" s="4">
         <v>17981532805</v>
@@ -9199,42 +9185,42 @@
     </row>
     <row r="104" spans="2:8" ht="14.45" customHeight="1">
       <c r="B104" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>508</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="14.45" customHeight="1">
       <c r="B105" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>322</v>
@@ -9245,91 +9231,91 @@
     </row>
     <row r="106" spans="2:8" ht="14.45" customHeight="1">
       <c r="B106" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="14.45" customHeight="1">
       <c r="B107" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="14.45" customHeight="1">
       <c r="B108" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E108" s="3" t="s">
+      <c r="G108" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="14.45" customHeight="1">
       <c r="B109" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="F109" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C109" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E109" s="3" t="s">
+      <c r="G109" s="4" t="s">
         <v>534</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>536</v>
       </c>
       <c r="H109" s="4">
         <v>17981692483</v>
@@ -9337,177 +9323,177 @@
     </row>
     <row r="110" spans="2:8" ht="14.45" customHeight="1">
       <c r="B110" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>539</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="14.45" customHeight="1">
       <c r="B111" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="14.45" customHeight="1">
       <c r="B112" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="14.45" customHeight="1">
       <c r="B113" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="14.45" customHeight="1">
       <c r="B114" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="F114" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="D114" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E114" s="3" t="s">
+      <c r="G114" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="14.45" customHeight="1">
       <c r="B115" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>564</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="14.45" customHeight="1">
       <c r="B116" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="D116" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="G116" s="14" t="s">
         <v>569</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="H116" s="14" t="s">
         <v>570</v>
-      </c>
-      <c r="G116" s="14" t="s">
-        <v>571</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="14.45" customHeight="1">
       <c r="B117" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>575</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>9</v>
@@ -9516,27 +9502,27 @@
         <v>126</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="14.45" customHeight="1">
       <c r="B118" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>579</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H118" s="7">
         <v>1732247602</v>
@@ -9544,25 +9530,25 @@
     </row>
     <row r="119" spans="2:8" ht="14.45" customHeight="1">
       <c r="B119" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E119" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>583</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="14.45" customHeight="1">
@@ -9570,13 +9556,13 @@
         <v>122</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>15</v>
@@ -9586,207 +9572,207 @@
     </row>
     <row r="121" spans="2:8" ht="14.45" customHeight="1">
       <c r="B121" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>590</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="14.45" customHeight="1">
       <c r="B122" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>595</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.45" customHeight="1">
       <c r="B123" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="E123" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="14.45" customHeight="1">
       <c r="B124" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G124" s="15"/>
       <c r="H124" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="14.45" customHeight="1">
       <c r="B125" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="14.45" customHeight="1">
       <c r="B126" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>616</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="14.45" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>621</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="14.45" customHeight="1">
       <c r="B128" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="14.45" customHeight="1">
       <c r="B129" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>632</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>143</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="14.45" customHeight="1"/>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD4D996-8FCF-4E7C-96E4-D918924B8E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1EF7DD-9AEA-4E2C-9F11-E41B4924C9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11595" yWindow="345" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="653">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -6330,13 +6330,16 @@
   </si>
   <si>
     <t>Rua Izaltina de Oliveira Pandim, 15 - Estancia Manacaz – Distrito Engenheiro Schimidt</t>
+  </si>
+  <si>
+    <t>R. Izaltina de Oliveira Padim, 15 - Estancia manacas, São José do Rio Preto - SP, 15062-060</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6392,6 +6395,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6413,7 +6422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6463,6 +6472,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8427,6 +8437,9 @@
       <c r="H70" s="4" t="s">
         <v>350</v>
       </c>
+      <c r="I70" s="17" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1EF7DD-9AEA-4E2C-9F11-E41B4924C9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD038C7B-0C4A-4CA2-B9E7-01DECC15B48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -6320,9 +6320,6 @@
     <t>Ass.Espirita Benef. Maria de Nazareth</t>
   </si>
   <si>
-    <t>Schimidt-SP</t>
-  </si>
-  <si>
     <t>Ass. Beneficente e Educacional Meimei - Abem</t>
   </si>
   <si>
@@ -6333,6 +6330,9 @@
   </si>
   <si>
     <t>R. Izaltina de Oliveira Padim, 15 - Estancia manacas, São José do Rio Preto - SP, 15062-060</t>
+  </si>
+  <si>
+    <t>Estancia Manacaz-SP</t>
   </si>
 </sst>
 </file>
@@ -8420,13 +8420,13 @@
         <v>643</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
@@ -8438,7 +8438,7 @@
         <v>350</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
@@ -8538,7 +8538,7 @@
         <v>370</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>642</v>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD038C7B-0C4A-4CA2-B9E7-01DECC15B48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4A7D7F-6C2E-4227-85E4-20B00267F95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -6326,13 +6326,13 @@
     <t>Ass.Esp.Ben.Caminho da Esperança</t>
   </si>
   <si>
-    <t>Rua Izaltina de Oliveira Pandim, 15 - Estancia Manacaz – Distrito Engenheiro Schimidt</t>
-  </si>
-  <si>
     <t>R. Izaltina de Oliveira Padim, 15 - Estancia manacas, São José do Rio Preto - SP, 15062-060</t>
   </si>
   <si>
     <t>Estancia Manacaz-SP</t>
+  </si>
+  <si>
+    <t>Rua Izaltina de Oliveira Pandim,15 - Distrito Engenheiro Schimidt</t>
   </si>
 </sst>
 </file>
@@ -8423,10 +8423,10 @@
         <v>648</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>652</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>650</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
@@ -8438,7 +8438,7 @@
         <v>350</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4A7D7F-6C2E-4227-85E4-20B00267F95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2511385-C655-43E0-9CFA-183DBD63D7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2511385-C655-43E0-9CFA-183DBD63D7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89BAE87-6879-4E94-B025-21EC141CCCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="652">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -6305,9 +6305,6 @@
     <t>São José do Rio Preto-SP</t>
   </si>
   <si>
-    <t>Meimei (Schimidt)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Toda segunda 5ª feira </t>
   </si>
   <si>
@@ -6329,10 +6326,10 @@
     <t>R. Izaltina de Oliveira Padim, 15 - Estancia manacas, São José do Rio Preto - SP, 15062-060</t>
   </si>
   <si>
-    <t>Estancia Manacaz-SP</t>
-  </si>
-  <si>
-    <t>Rua Izaltina de Oliveira Pandim,15 - Distrito Engenheiro Schimidt</t>
+    <t xml:space="preserve">Rua Izaltina de Oliveira Pandim,15 </t>
+  </si>
+  <si>
+    <t>Schmidt-SP</t>
   </si>
 </sst>
 </file>
@@ -6853,7 +6850,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
@@ -7184,7 +7181,7 @@
         <v>84</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>85</v>
@@ -7543,7 +7540,7 @@
         <v>165</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>136</v>
@@ -8416,17 +8413,15 @@
       </c>
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B70" s="8" t="s">
-        <v>643</v>
-      </c>
+      <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>651</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
@@ -8438,7 +8433,7 @@
         <v>350</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
@@ -8538,7 +8533,7 @@
         <v>370</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>642</v>
@@ -9316,7 +9311,7 @@
         <v>531</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>642</v>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89BAE87-6879-4E94-B025-21EC141CCCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2EF142-2478-40BE-82ED-85D19775DB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="653">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -6326,10 +6326,13 @@
     <t>R. Izaltina de Oliveira Padim, 15 - Estancia manacas, São José do Rio Preto - SP, 15062-060</t>
   </si>
   <si>
-    <t xml:space="preserve">Rua Izaltina de Oliveira Pandim,15 </t>
-  </si>
-  <si>
     <t>Schmidt-SP</t>
+  </si>
+  <si>
+    <t>Rua Izaltina de Oliveira Pandim,15  Estancia Manacaz - Egenheiro Schimdt</t>
+  </si>
+  <si>
+    <t>Rua Alexandre Rosa 156 - Vila São Pedro</t>
   </si>
 </sst>
 </file>
@@ -8418,10 +8421,10 @@
         <v>647</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>651</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>650</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
@@ -8584,8 +8587,8 @@
       <c r="D77" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>382</v>
+      <c r="E77" s="8" t="s">
+        <v>652</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>383</v>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2EF142-2478-40BE-82ED-85D19775DB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745284D4-0D29-4F29-AA02-1628EC9D11C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745284D4-0D29-4F29-AA02-1628EC9D11C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA6F416-4142-47B0-8A0A-255228B12EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="652">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -6321,9 +6321,6 @@
   </si>
   <si>
     <t>Ass.Esp.Ben.Caminho da Esperança</t>
-  </si>
-  <si>
-    <t>R. Izaltina de Oliveira Padim, 15 - Estancia manacas, São José do Rio Preto - SP, 15062-060</t>
   </si>
   <si>
     <t>Schmidt-SP</t>
@@ -8421,10 +8418,10 @@
         <v>647</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>650</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>651</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
@@ -8435,9 +8432,7 @@
       <c r="H70" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="I70" s="17" t="s">
-        <v>649</v>
-      </c>
+      <c r="I70" s="17"/>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
@@ -8588,7 +8583,7 @@
         <v>642</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>383</v>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA6F416-4142-47B0-8A0A-255228B12EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B046E6-0638-42D4-947C-A628CE34710F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="11280" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="653">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -6330,6 +6330,9 @@
   </si>
   <si>
     <t>Rua Alexandre Rosa 156 - Vila São Pedro</t>
+  </si>
+  <si>
+    <t>Meimei (Schimidt)</t>
   </si>
 </sst>
 </file>
@@ -8413,7 +8416,9 @@
       </c>
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
-      <c r="B70" s="8"/>
+      <c r="B70" s="8" t="s">
+        <v>652</v>
+      </c>
       <c r="C70" s="8" t="s">
         <v>647</v>
       </c>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B046E6-0638-42D4-947C-A628CE34710F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0D2CC3-D1A9-4B81-82CC-D6D2F553443F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="0" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="2520" yWindow="150" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -980,9 +980,6 @@
     </r>
   </si>
   <si>
-    <t>Rua Siqueira Campos 250</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -6333,6 +6330,9 @@
   </si>
   <si>
     <t>Meimei (Schimidt)</t>
+  </si>
+  <si>
+    <t>R. Siqueira Campos 250</t>
   </si>
 </sst>
 </file>
@@ -6824,28 +6824,28 @@
   <sheetData>
     <row r="1" spans="2:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="14.45" customHeight="1">
@@ -6853,7 +6853,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
@@ -7184,7 +7184,7 @@
         <v>84</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>85</v>
@@ -7250,13 +7250,13 @@
         <v>93</v>
       </c>
       <c r="E19" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="H19" s="4">
         <v>17991385400</v>
@@ -7264,22 +7264,22 @@
     </row>
     <row r="20" spans="2:8" ht="14.45" customHeight="1">
       <c r="B20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="H20" s="7">
         <v>17992731001</v>
@@ -7287,68 +7287,68 @@
     </row>
     <row r="21" spans="2:8" ht="14.45" customHeight="1">
       <c r="B21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="14.45" customHeight="1">
       <c r="B22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="14.45" customHeight="1">
       <c r="B23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H23" s="4">
         <v>17991019999</v>
@@ -7356,68 +7356,68 @@
     </row>
     <row r="24" spans="2:8" ht="14.45" customHeight="1">
       <c r="B24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14.45" customHeight="1">
       <c r="B25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="14.45" customHeight="1">
       <c r="B26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="H26" s="7">
         <v>17996487770</v>
@@ -7425,22 +7425,22 @@
     </row>
     <row r="27" spans="2:8" ht="14.45" customHeight="1">
       <c r="B27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="H27" s="4">
         <v>17991436228</v>
@@ -7448,45 +7448,45 @@
     </row>
     <row r="28" spans="2:8" ht="14.45" customHeight="1">
       <c r="B28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="14.45" customHeight="1">
       <c r="B29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H29" s="4">
         <v>17981671066</v>
@@ -7494,22 +7494,22 @@
     </row>
     <row r="30" spans="2:8" ht="14.45" customHeight="1">
       <c r="B30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="H30" s="7">
         <v>17997685797</v>
@@ -7517,45 +7517,45 @@
     </row>
     <row r="31" spans="2:8" ht="14.45" customHeight="1">
       <c r="B31" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G31" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="14.45" customHeight="1">
       <c r="B32" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H32" s="7">
         <v>17996369299</v>
@@ -7563,22 +7563,22 @@
     </row>
     <row r="33" spans="2:8" ht="14.45" customHeight="1">
       <c r="B33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="H33" s="4">
         <v>17992296835</v>
@@ -7586,22 +7586,22 @@
     </row>
     <row r="34" spans="2:8" ht="14.45" customHeight="1">
       <c r="B34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H34" s="7">
         <v>17997762047</v>
@@ -7609,22 +7609,22 @@
     </row>
     <row r="35" spans="2:8" ht="14.45" customHeight="1">
       <c r="B35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H35" s="4">
         <v>17988298392</v>
@@ -7632,22 +7632,22 @@
     </row>
     <row r="36" spans="2:8" ht="14.45" customHeight="1">
       <c r="B36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H36" s="7">
         <v>17988082952</v>
@@ -7655,22 +7655,22 @@
     </row>
     <row r="37" spans="2:8" ht="14.45" customHeight="1">
       <c r="B37" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H37" s="4">
         <v>17996170113</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="38" spans="2:8" ht="14.45" customHeight="1">
       <c r="B38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H38" s="7">
         <v>17991133571</v>
@@ -7701,22 +7701,22 @@
     </row>
     <row r="39" spans="2:8" ht="14.45" customHeight="1">
       <c r="B39" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H39" s="4">
         <v>17997196510</v>
@@ -7724,45 +7724,45 @@
     </row>
     <row r="40" spans="2:8" ht="14.45" customHeight="1">
       <c r="B40" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.45" customHeight="1">
       <c r="B41" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H41" s="4">
         <v>17997212303</v>
@@ -7770,45 +7770,45 @@
     </row>
     <row r="42" spans="2:8" ht="14.45" customHeight="1">
       <c r="B42" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.45" customHeight="1">
       <c r="B43" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="H43" s="4">
         <v>17981170059</v>
@@ -7816,45 +7816,45 @@
     </row>
     <row r="44" spans="2:8" ht="14.45" customHeight="1">
       <c r="B44" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G44" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.45" customHeight="1">
       <c r="B45" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H45" s="4">
         <v>17996015188</v>
@@ -7862,68 +7862,68 @@
     </row>
     <row r="46" spans="2:8" ht="14.45" customHeight="1">
       <c r="B46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.45" customHeight="1">
       <c r="B47" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.45" customHeight="1">
       <c r="B48" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="H48" s="7">
         <v>17992170608</v>
@@ -7931,91 +7931,91 @@
     </row>
     <row r="49" spans="2:8" ht="14.45" customHeight="1">
       <c r="B49" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="14.45" customHeight="1">
       <c r="B50" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G50" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="14.45" customHeight="1">
       <c r="B51" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G51" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="14.45" customHeight="1">
       <c r="B52" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H52" s="7">
         <v>1732818196</v>
@@ -8023,137 +8023,137 @@
     </row>
     <row r="53" spans="2:8" ht="14.45" customHeight="1">
       <c r="B53" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="H53" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="14.45" customHeight="1">
       <c r="B54" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="14.45" customHeight="1">
       <c r="B55" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="14.45" customHeight="1">
       <c r="B56" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D56" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G56" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H56" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="14.45" customHeight="1">
       <c r="B57" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D57" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="14.45" customHeight="1">
       <c r="B58" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H58" s="7">
         <v>17997283279</v>
@@ -8161,91 +8161,91 @@
     </row>
     <row r="59" spans="2:8" ht="14.45" customHeight="1">
       <c r="B59" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G59" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="14.45" customHeight="1">
       <c r="B60" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G60" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="14.45" customHeight="1">
       <c r="B61" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="H61" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="14.45" customHeight="1">
       <c r="B62" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H62" s="7">
         <v>17997110972</v>
@@ -8253,68 +8253,68 @@
     </row>
     <row r="63" spans="2:8" ht="14.45" customHeight="1">
       <c r="B63" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="14.45" customHeight="1">
       <c r="B64" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G64" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="14.45" customHeight="1">
       <c r="B65" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="G65" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="H65" s="4">
         <v>1732351010</v>
@@ -8322,141 +8322,141 @@
     </row>
     <row r="66" spans="2:9" ht="14.45" customHeight="1">
       <c r="B66" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="D66" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G66" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="H66" s="4" t="s">
-        <v>332</v>
-      </c>
       <c r="I66" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="14.45" customHeight="1">
       <c r="B67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="G67" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="14.45" customHeight="1">
       <c r="B68" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="69" spans="2:9" ht="14.45" customHeight="1">
       <c r="B69" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="H69" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
       <c r="B70" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>649</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>650</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G70" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="I70" s="17"/>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="H71" s="4">
         <v>17997727089</v>
@@ -8464,206 +8464,206 @@
     </row>
     <row r="72" spans="2:9" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G72" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G74" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G75" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>381</v>
-      </c>
       <c r="D77" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F77" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G79" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H80" s="7">
         <v>17991167827</v>
@@ -8671,137 +8671,137 @@
     </row>
     <row r="81" spans="2:8" ht="14.45" customHeight="1">
       <c r="B81" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="14.45" customHeight="1">
       <c r="B82" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>409</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="14.45" customHeight="1">
       <c r="B83" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>414</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G83" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="14.45" customHeight="1">
       <c r="B84" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G84" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="14.45" customHeight="1">
       <c r="B85" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E85" s="3" t="s">
+      <c r="F85" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G85" s="4" t="s">
+      <c r="H85" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="14.45" customHeight="1">
       <c r="B86" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H86" s="7">
         <v>17996021994</v>
@@ -8809,22 +8809,22 @@
     </row>
     <row r="87" spans="2:8" ht="14.45" customHeight="1">
       <c r="B87" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D87" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E87" s="3" t="s">
+      <c r="F87" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>434</v>
       </c>
       <c r="H87" s="4">
         <v>17991251239</v>
@@ -8832,160 +8832,160 @@
     </row>
     <row r="88" spans="2:8" ht="14.45" customHeight="1">
       <c r="B88" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>437</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G88" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="14.45" customHeight="1">
       <c r="B89" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="D89" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="G89" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="14.45" customHeight="1">
       <c r="B90" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G90" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="H90" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="14.45" customHeight="1">
       <c r="B91" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="D91" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G91" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="14.45" customHeight="1">
       <c r="B92" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="14.45" customHeight="1">
       <c r="B93" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="D93" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G93" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="14.45" customHeight="1">
       <c r="B94" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H94" s="7">
         <v>1732348032</v>
@@ -8993,22 +8993,22 @@
     </row>
     <row r="95" spans="2:8" ht="14.45" customHeight="1">
       <c r="B95" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H95" s="4">
         <v>17996684410</v>
@@ -9016,131 +9016,131 @@
     </row>
     <row r="96" spans="2:8" ht="14.45" customHeight="1">
       <c r="B96" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G96" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="H96" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="14.45" customHeight="1">
       <c r="B97" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D97" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="F97" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="G97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="14.45" customHeight="1">
       <c r="B98" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="D98" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="14.45" customHeight="1">
       <c r="B99" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>491</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G99" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="14.45" customHeight="1">
       <c r="B100" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="D100" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H100" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="14.45" customHeight="1">
       <c r="B101" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>9</v>
@@ -9156,7 +9156,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>2</v>
@@ -9173,22 +9173,22 @@
     </row>
     <row r="103" spans="2:8" ht="14.45" customHeight="1">
       <c r="B103" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H103" s="4">
         <v>17981532805</v>
@@ -9196,137 +9196,137 @@
     </row>
     <row r="104" spans="2:8" ht="14.45" customHeight="1">
       <c r="B104" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="D104" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G104" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="14.45" customHeight="1">
       <c r="B105" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="D105" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="F105" s="4" t="s">
-        <v>514</v>
-      </c>
       <c r="G105" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="H105" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="14.45" customHeight="1">
       <c r="B106" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="D106" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>517</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="H106" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="14.45" customHeight="1">
       <c r="B107" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G107" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="H107" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="14.45" customHeight="1">
       <c r="B108" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="D108" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="G108" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="14.45" customHeight="1">
       <c r="B109" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="C109" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="G109" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>534</v>
       </c>
       <c r="H109" s="4">
         <v>17981692483</v>
@@ -9334,206 +9334,206 @@
     </row>
     <row r="110" spans="2:8" ht="14.45" customHeight="1">
       <c r="B110" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="D110" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G110" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>538</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="14.45" customHeight="1">
       <c r="B111" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="D111" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>541</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>542</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G111" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="14.45" customHeight="1">
       <c r="B112" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G112" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="14.45" customHeight="1">
       <c r="B113" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>551</v>
-      </c>
       <c r="D113" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G113" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H113" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="14.45" customHeight="1">
       <c r="B114" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="D114" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="D114" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E114" s="3" t="s">
+      <c r="F114" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="G114" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="14.45" customHeight="1">
       <c r="B115" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G115" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="14.45" customHeight="1">
       <c r="B116" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D116" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="G116" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="G116" s="14" t="s">
+      <c r="H116" s="14" t="s">
         <v>569</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="14.45" customHeight="1">
       <c r="B117" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="D117" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>573</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="14.45" customHeight="1">
       <c r="B118" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H118" s="7">
         <v>1732247602</v>
@@ -9541,39 +9541,39 @@
     </row>
     <row r="119" spans="2:8" ht="14.45" customHeight="1">
       <c r="B119" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E119" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>582</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="14.45" customHeight="1">
       <c r="B120" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C120" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>15</v>
@@ -9583,207 +9583,207 @@
     </row>
     <row r="121" spans="2:8" ht="14.45" customHeight="1">
       <c r="B121" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G121" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="14.45" customHeight="1">
       <c r="B122" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>593</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G122" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.45" customHeight="1">
       <c r="B123" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E123" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>599</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="14.45" customHeight="1">
       <c r="B124" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="E124" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G124" s="15"/>
       <c r="H124" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="14.45" customHeight="1">
       <c r="B125" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="D125" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>609</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G125" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="H125" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="14.45" customHeight="1">
       <c r="B126" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="D126" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>613</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G126" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="14.45" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>618</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>619</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G127" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>620</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="14.45" customHeight="1">
       <c r="B128" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="E128" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>625</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G128" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="H128" s="4" t="s">
         <v>626</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="14.45" customHeight="1">
       <c r="B129" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="D129" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>630</v>
-      </c>
       <c r="F129" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G129" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>626</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="14.45" customHeight="1"/>

--- a/guia.xlsx
+++ b/guia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trader\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0D2CC3-D1A9-4B81-82CC-D6D2F553443F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078CBDD6-BFC4-4AEA-96D2-E65D3ED7E6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="150" windowWidth="26910" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
+    <workbookView xWindow="210" yWindow="360" windowWidth="34335" windowHeight="15435" xr2:uid="{FAC3933B-D575-4B88-AFE4-E20BB420EB64}"/>
   </bookViews>
   <sheets>
     <sheet name="casas espiritas python" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="656">
   <si>
     <t>Nome fantasia do Centro Espírita</t>
   </si>
@@ -886,16 +886,6 @@
         <rFont val="Arial MT"/>
         <family val="2"/>
       </rPr>
-      <t>Rua João Antonio Bispo, 40 - Vila Terruge</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial MT"/>
-        <family val="2"/>
-      </rPr>
       <t>Franciele</t>
     </r>
   </si>
@@ -6296,9 +6286,6 @@
     <t>R. Nagib Abissamira - Res. Ana Célia, São José do Rio Preto - SP, 15045-500</t>
   </si>
   <si>
-    <t>NOME GOOGLE MAPS</t>
-  </si>
-  <si>
     <t>São José do Rio Preto-SP</t>
   </si>
   <si>
@@ -6333,13 +6320,39 @@
   </si>
   <si>
     <t>R. Siqueira Campos 250</t>
+  </si>
+  <si>
+    <t>Rua Edmar Gonçalves 207 (Zona Rural Estância - São Carlos, São José do Rio Preto - SP, 15052-864</t>
+  </si>
+  <si>
+    <t>Rua João Antonio Bispo, 40 - Vila Terruge</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rua: João Antonio Bispo, 427 - Vila irmãos terrugi, Icém - SP, 15460-000</t>
+    </r>
+  </si>
+  <si>
+    <t>R. dos Tozzo, 1140 - Conj. Hab. Floriano Rissi, Mirassol - SP, 15130-000</t>
+  </si>
+  <si>
+    <t>MAPAS GOOGLE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6401,6 +6414,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6422,7 +6442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6473,6 +6493,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6824,28 +6845,28 @@
   <sheetData>
     <row r="1" spans="2:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="14.45" customHeight="1">
@@ -6853,7 +6874,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
@@ -7184,7 +7205,7 @@
         <v>84</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>85</v>
@@ -7193,7 +7214,7 @@
         <v>17981625858</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14.45" customHeight="1">
+    <row r="17" spans="2:9" ht="14.45" customHeight="1">
       <c r="B17" s="3" t="s">
         <v>86</v>
       </c>
@@ -7203,359 +7224,365 @@
       <c r="D17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>88</v>
+      <c r="E17" s="8" t="s">
+        <v>652</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="18" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B18" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H18" s="7">
         <v>1732699990</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14.45" customHeight="1">
+    <row r="19" spans="2:9" ht="14.45" customHeight="1">
       <c r="B19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="H19" s="4">
         <v>17991385400</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="14.45" customHeight="1">
+    <row r="20" spans="2:9" ht="14.45" customHeight="1">
       <c r="B20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="H20" s="7">
         <v>17992731001</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="14.45" customHeight="1">
+    <row r="21" spans="2:9" ht="14.45" customHeight="1">
       <c r="B21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H21" s="4" t="s">
+    </row>
+    <row r="22" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B22" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H22" s="4" t="s">
+    </row>
+    <row r="23" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B23" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H23" s="4">
         <v>17991019999</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14.45" customHeight="1">
+    <row r="24" spans="2:9" ht="14.45" customHeight="1">
       <c r="B24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H24" s="4" t="s">
+    </row>
+    <row r="25" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B25" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H25" s="4" t="s">
+    </row>
+    <row r="26" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B26" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="26" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="H26" s="7">
         <v>17996487770</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14.45" customHeight="1">
+    <row r="27" spans="2:9" ht="14.45" customHeight="1">
       <c r="B27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="H27" s="4">
         <v>17991436228</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14.45" customHeight="1">
+    <row r="28" spans="2:9" ht="14.45" customHeight="1">
       <c r="B28" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H28" s="4" t="s">
+    </row>
+    <row r="29" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B29" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H29" s="4">
         <v>17981671066</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="14.45" customHeight="1">
+    <row r="30" spans="2:9" ht="14.45" customHeight="1">
       <c r="B30" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="H30" s="7">
         <v>17997685797</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14.45" customHeight="1">
+    <row r="31" spans="2:9" ht="14.45" customHeight="1">
       <c r="B31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G31" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="I31" s="6" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B32" s="3" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="32" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H32" s="7">
         <v>17996369299</v>
@@ -7563,22 +7590,22 @@
     </row>
     <row r="33" spans="2:8" ht="14.45" customHeight="1">
       <c r="B33" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="H33" s="4">
         <v>17992296835</v>
@@ -7586,22 +7613,22 @@
     </row>
     <row r="34" spans="2:8" ht="14.45" customHeight="1">
       <c r="B34" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H34" s="7">
         <v>17997762047</v>
@@ -7609,22 +7636,22 @@
     </row>
     <row r="35" spans="2:8" ht="14.45" customHeight="1">
       <c r="B35" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H35" s="4">
         <v>17988298392</v>
@@ -7632,22 +7659,22 @@
     </row>
     <row r="36" spans="2:8" ht="14.45" customHeight="1">
       <c r="B36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H36" s="7">
         <v>17988082952</v>
@@ -7655,22 +7682,22 @@
     </row>
     <row r="37" spans="2:8" ht="14.45" customHeight="1">
       <c r="B37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H37" s="4">
         <v>17996170113</v>
@@ -7678,22 +7705,22 @@
     </row>
     <row r="38" spans="2:8" ht="14.45" customHeight="1">
       <c r="B38" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H38" s="7">
         <v>17991133571</v>
@@ -7701,22 +7728,22 @@
     </row>
     <row r="39" spans="2:8" ht="14.45" customHeight="1">
       <c r="B39" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H39" s="4">
         <v>17997196510</v>
@@ -7724,45 +7751,45 @@
     </row>
     <row r="40" spans="2:8" ht="14.45" customHeight="1">
       <c r="B40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.45" customHeight="1">
       <c r="B41" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H41" s="4">
         <v>17997212303</v>
@@ -7770,45 +7797,45 @@
     </row>
     <row r="42" spans="2:8" ht="14.45" customHeight="1">
       <c r="B42" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.45" customHeight="1">
       <c r="B43" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="H43" s="4">
         <v>17981170059</v>
@@ -7816,45 +7843,45 @@
     </row>
     <row r="44" spans="2:8" ht="14.45" customHeight="1">
       <c r="B44" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G44" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.45" customHeight="1">
       <c r="B45" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H45" s="4">
         <v>17996015188</v>
@@ -7862,68 +7889,68 @@
     </row>
     <row r="46" spans="2:8" ht="14.45" customHeight="1">
       <c r="B46" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.45" customHeight="1">
       <c r="B47" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.45" customHeight="1">
       <c r="B48" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="H48" s="7">
         <v>17992170608</v>
@@ -7931,91 +7958,91 @@
     </row>
     <row r="49" spans="2:8" ht="14.45" customHeight="1">
       <c r="B49" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="14.45" customHeight="1">
       <c r="B50" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G50" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="14.45" customHeight="1">
       <c r="B51" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G51" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="14.45" customHeight="1">
       <c r="B52" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H52" s="7">
         <v>1732818196</v>
@@ -8023,137 +8050,137 @@
     </row>
     <row r="53" spans="2:8" ht="14.45" customHeight="1">
       <c r="B53" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="H53" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="14.45" customHeight="1">
       <c r="B54" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="14.45" customHeight="1">
       <c r="B55" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="14.45" customHeight="1">
       <c r="B56" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>277</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G56" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H56" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="14.45" customHeight="1">
       <c r="B57" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D57" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="14.45" customHeight="1">
       <c r="B58" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H58" s="7">
         <v>17997283279</v>
@@ -8161,91 +8188,91 @@
     </row>
     <row r="59" spans="2:8" ht="14.45" customHeight="1">
       <c r="B59" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G59" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="14.45" customHeight="1">
       <c r="B60" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G60" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="14.45" customHeight="1">
       <c r="B61" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="H61" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="14.45" customHeight="1">
       <c r="B62" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H62" s="7">
         <v>17997110972</v>
@@ -8253,68 +8280,68 @@
     </row>
     <row r="63" spans="2:8" ht="14.45" customHeight="1">
       <c r="B63" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="14.45" customHeight="1">
       <c r="B64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G64" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="14.45" customHeight="1">
       <c r="B65" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="G65" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="H65" s="4">
         <v>1732351010</v>
@@ -8322,141 +8349,141 @@
     </row>
     <row r="66" spans="2:9" ht="14.45" customHeight="1">
       <c r="B66" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="D66" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G66" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="H66" s="4" t="s">
-        <v>331</v>
-      </c>
       <c r="I66" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="14.45" customHeight="1">
       <c r="B67" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="G67" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="14.45" customHeight="1">
       <c r="B68" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="69" spans="2:9" ht="14.45" customHeight="1">
       <c r="B69" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="H69" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="14.45" customHeight="1">
       <c r="B70" s="8" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C70" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="D70" s="9" t="s">
         <v>646</v>
       </c>
-      <c r="D70" s="9" t="s">
-        <v>648</v>
-      </c>
       <c r="E70" s="8" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G70" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="I70" s="17"/>
     </row>
     <row r="71" spans="2:9" ht="14.45" customHeight="1">
       <c r="B71" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="H71" s="4">
         <v>17997727089</v>
@@ -8464,206 +8491,206 @@
     </row>
     <row r="72" spans="2:9" ht="14.45" customHeight="1">
       <c r="B72" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G72" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="14.45" customHeight="1">
       <c r="B73" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="14.45" customHeight="1">
       <c r="B74" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G74" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="14.45" customHeight="1">
       <c r="B75" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G75" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="14.45" customHeight="1">
       <c r="B76" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14.45" customHeight="1">
       <c r="B77" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>380</v>
-      </c>
       <c r="D77" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F77" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="14.45" customHeight="1">
       <c r="B78" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="14.45" customHeight="1">
       <c r="B79" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G79" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="14.45" customHeight="1">
       <c r="B80" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H80" s="7">
         <v>17991167827</v>
@@ -8671,137 +8698,137 @@
     </row>
     <row r="81" spans="2:8" ht="14.45" customHeight="1">
       <c r="B81" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="14.45" customHeight="1">
       <c r="B82" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="14.45" customHeight="1">
       <c r="B83" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>413</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G83" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="14.45" customHeight="1">
       <c r="B84" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G84" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="14.45" customHeight="1">
       <c r="B85" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E85" s="3" t="s">
+      <c r="F85" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G85" s="4" t="s">
+      <c r="H85" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="14.45" customHeight="1">
       <c r="B86" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>428</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H86" s="7">
         <v>17996021994</v>
@@ -8809,22 +8836,22 @@
     </row>
     <row r="87" spans="2:8" ht="14.45" customHeight="1">
       <c r="B87" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D87" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E87" s="3" t="s">
+      <c r="F87" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="H87" s="4">
         <v>17991251239</v>
@@ -8832,160 +8859,160 @@
     </row>
     <row r="88" spans="2:8" ht="14.45" customHeight="1">
       <c r="B88" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G88" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="14.45" customHeight="1">
       <c r="B89" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D89" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="G89" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="14.45" customHeight="1">
       <c r="B90" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G90" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="H90" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="14.45" customHeight="1">
       <c r="B91" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="D91" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G91" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="14.45" customHeight="1">
       <c r="B92" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="14.45" customHeight="1">
       <c r="B93" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="D93" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G93" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="14.45" customHeight="1">
       <c r="B94" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H94" s="7">
         <v>1732348032</v>
@@ -8993,22 +9020,22 @@
     </row>
     <row r="95" spans="2:8" ht="14.45" customHeight="1">
       <c r="B95" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>472</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H95" s="4">
         <v>17996684410</v>
@@ -9016,131 +9043,131 @@
     </row>
     <row r="96" spans="2:8" ht="14.45" customHeight="1">
       <c r="B96" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G96" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="H96" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="H96" s="4" t="s">
+    </row>
+    <row r="97" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B97" s="3" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="97" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="D97" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="F97" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="G97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="H97" s="4" t="s">
+    </row>
+    <row r="98" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B98" s="3" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="98" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="D98" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>485</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="H98" s="4" t="s">
+    </row>
+    <row r="99" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B99" s="3" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="99" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>489</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>490</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G99" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H99" s="4" t="s">
+    </row>
+    <row r="100" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B100" s="3" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="100" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="D100" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>495</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="H100" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="H100" s="4" t="s">
+    </row>
+    <row r="101" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B101" s="3" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="101" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>9</v>
@@ -9148,7 +9175,7 @@
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
     </row>
-    <row r="102" spans="2:8" ht="14.45" hidden="1" customHeight="1">
+    <row r="102" spans="2:9" ht="14.45" hidden="1" customHeight="1">
       <c r="B102" s="10" t="s">
         <v>0</v>
       </c>
@@ -9156,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>2</v>
@@ -9171,369 +9198,372 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="14.45" customHeight="1">
+    <row r="103" spans="2:9" ht="14.45" customHeight="1">
       <c r="B103" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>502</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>503</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H103" s="4">
         <v>17981532805</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="14.45" customHeight="1">
+    <row r="104" spans="2:9" ht="14.45" customHeight="1">
       <c r="B104" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="D104" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G104" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="H104" s="4" t="s">
+    </row>
+    <row r="105" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B105" s="3" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="105" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="D105" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="G105" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B106" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="G105" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="D106" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="H106" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="H106" s="4" t="s">
+    </row>
+    <row r="107" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B107" s="3" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="107" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B107" s="3" t="s">
+      <c r="C107" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>521</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G107" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="H107" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="H107" s="4" t="s">
+    </row>
+    <row r="108" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B108" s="3" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="108" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="D108" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="G108" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="H108" s="4" t="s">
+    </row>
+    <row r="109" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B109" s="3" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="109" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B109" s="3" t="s">
+      <c r="C109" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C109" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="G109" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>533</v>
       </c>
       <c r="H109" s="4">
         <v>17981692483</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="14.45" customHeight="1">
+    <row r="110" spans="2:9" ht="14.45" customHeight="1">
       <c r="B110" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="D110" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G110" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="H110" s="4" t="s">
+    </row>
+    <row r="111" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B111" s="3" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="111" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B111" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="D111" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G111" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="H111" s="4" t="s">
+      <c r="I111" s="6" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" ht="14.45" customHeight="1">
+      <c r="B112" s="3" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="112" spans="2:8" ht="14.45" customHeight="1">
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G112" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="14.45" customHeight="1">
       <c r="B113" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>550</v>
-      </c>
       <c r="D113" s="9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G113" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="H113" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="14.45" customHeight="1">
       <c r="B114" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="D114" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="D114" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E114" s="3" t="s">
+      <c r="F114" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="G114" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="14.45" customHeight="1">
       <c r="B115" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G115" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="14.45" customHeight="1">
       <c r="B116" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="D116" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="G116" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="G116" s="14" t="s">
+      <c r="H116" s="14" t="s">
         <v>568</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="14.45" customHeight="1">
       <c r="B117" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="D117" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="14.45" customHeight="1">
       <c r="B118" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H118" s="7">
         <v>1732247602</v>
@@ -9541,39 +9571,39 @@
     </row>
     <row r="119" spans="2:8" ht="14.45" customHeight="1">
       <c r="B119" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E119" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>580</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>581</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="14.45" customHeight="1">
       <c r="B120" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C120" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>15</v>
@@ -9583,212 +9613,213 @@
     </row>
     <row r="121" spans="2:8" ht="14.45" customHeight="1">
       <c r="B121" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>587</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G121" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>588</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="14.45" customHeight="1">
       <c r="B122" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G122" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.45" customHeight="1">
       <c r="B123" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E123" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>598</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>599</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="14.45" customHeight="1">
       <c r="B124" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="E124" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>604</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G124" s="15"/>
       <c r="H124" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="14.45" customHeight="1">
       <c r="B125" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="D125" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G125" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="H125" s="4" t="s">
         <v>609</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="14.45" customHeight="1">
       <c r="B126" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="D126" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>613</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G126" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>614</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="14.45" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>617</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>618</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G127" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>619</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="14.45" customHeight="1">
       <c r="B128" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="E128" s="3" t="s">
         <v>623</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>624</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G128" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="H128" s="4" t="s">
         <v>625</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="14.45" customHeight="1">
       <c r="B129" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="D129" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>629</v>
-      </c>
       <c r="F129" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G129" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>625</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="14.45" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
